--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,285 +396,285 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>606</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>133</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>95</v>
+        <v>440</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>126</v>
+        <v>615</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>97</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>143</v>
+        <v>949</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>173</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>145</v>
+        <v>1007</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>173</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>361</v>
+        <v>1654</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8">
-        <v>164</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>434</v>
+        <v>1656</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>435</v>
+        <v>2424</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C10">
-        <v>111</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>523</v>
+        <v>2497</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11">
-        <v>171</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>566</v>
+        <v>3475</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>589</v>
+        <v>3477</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>615</v>
+        <v>3495</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>111</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>624</v>
+        <v>3889</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>112</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>738</v>
+        <v>3955</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>788</v>
+        <v>4019</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>81</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>949</v>
+        <v>5453</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1309</v>
+        <v>5729</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1413</v>
+        <v>5730</v>
       </c>
       <c r="B20">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>114</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1414</v>
+        <v>6097</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C21">
-        <v>112</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1656</v>
+        <v>6931</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1668</v>
+        <v>8673</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>2049</v>
+        <v>8938</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>606</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>2436</v>
+        <v>10147</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>130</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>2438</v>
+        <v>11739</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>706</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>2991</v>
+        <v>11838</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>161</v>
@@ -682,40 +682,40 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>3495</v>
+        <v>11868</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
       <c r="C28">
-        <v>1127</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>3671</v>
+        <v>20927</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>99</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>3673</v>
+        <v>22325</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>270</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>3894</v>
+        <v>22327</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -726,574 +726,57 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>5111</v>
+        <v>23233</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C32">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>5453</v>
+        <v>23611</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>114</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>5490</v>
+        <v>23992</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C34">
-        <v>111</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>5577</v>
+        <v>24566</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>5584</v>
+        <v>24567</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37">
-        <v>5585</v>
-      </c>
-      <c r="B37">
-        <v>3</v>
-      </c>
-      <c r="C37">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38">
-        <v>5722</v>
-      </c>
-      <c r="B38">
-        <v>2</v>
-      </c>
-      <c r="C38">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39">
-        <v>5733</v>
-      </c>
-      <c r="B39">
-        <v>2</v>
-      </c>
-      <c r="C39">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40">
-        <v>6098</v>
-      </c>
-      <c r="B40">
-        <v>80</v>
-      </c>
-      <c r="C40">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41">
-        <v>6158</v>
-      </c>
-      <c r="B41">
-        <v>2</v>
-      </c>
-      <c r="C41">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42">
-        <v>6494</v>
-      </c>
-      <c r="B42">
-        <v>1</v>
-      </c>
-      <c r="C42">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43">
-        <v>6575</v>
-      </c>
-      <c r="B43">
-        <v>3</v>
-      </c>
-      <c r="C43">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44">
-        <v>7004</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45">
-        <v>8356</v>
-      </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46">
-        <v>8649</v>
-      </c>
-      <c r="B46">
-        <v>2</v>
-      </c>
-      <c r="C46">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47">
-        <v>8853</v>
-      </c>
-      <c r="B47">
-        <v>2</v>
-      </c>
-      <c r="C47">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48">
-        <v>9081</v>
-      </c>
-      <c r="B48">
-        <v>3</v>
-      </c>
-      <c r="C48">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49">
-        <v>10148</v>
-      </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50">
-        <v>10514</v>
-      </c>
-      <c r="B50">
-        <v>3</v>
-      </c>
-      <c r="C50">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51">
-        <v>10716</v>
-      </c>
-      <c r="B51">
-        <v>3</v>
-      </c>
-      <c r="C51">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52">
-        <v>11090</v>
-      </c>
-      <c r="B52">
-        <v>1</v>
-      </c>
-      <c r="C52">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53">
-        <v>11093</v>
-      </c>
-      <c r="B53">
-        <v>1</v>
-      </c>
-      <c r="C53">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54">
-        <v>11212</v>
-      </c>
-      <c r="B54">
-        <v>4</v>
-      </c>
-      <c r="C54">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55">
-        <v>11234</v>
-      </c>
-      <c r="B55">
-        <v>2</v>
-      </c>
-      <c r="C55">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56">
-        <v>11454</v>
-      </c>
-      <c r="B56">
-        <v>2</v>
-      </c>
-      <c r="C56">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57">
-        <v>11681</v>
-      </c>
-      <c r="B57">
-        <v>2</v>
-      </c>
-      <c r="C57">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58">
-        <v>11684</v>
-      </c>
-      <c r="B58">
-        <v>2</v>
-      </c>
-      <c r="C58">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59">
-        <v>11767</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60">
-        <v>11773</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61">
-        <v>11836</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
-      </c>
-      <c r="C61">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62">
-        <v>11837</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
-      </c>
-      <c r="C62">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63">
-        <v>11838</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-      <c r="C63">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64">
-        <v>11856</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
-      </c>
-      <c r="C64">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65">
-        <v>11858</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
-      </c>
-      <c r="C65">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66">
-        <v>11885</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
-      </c>
-      <c r="C66">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67">
-        <v>11886</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
-      <c r="C67">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68">
-        <v>11920</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69">
-        <v>12010</v>
-      </c>
-      <c r="B69">
-        <v>3</v>
-      </c>
-      <c r="C69">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70">
-        <v>12040</v>
-      </c>
-      <c r="B70">
-        <v>68</v>
-      </c>
-      <c r="C70">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71">
-        <v>12353</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
-      </c>
-      <c r="C71">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72">
-        <v>12791</v>
-      </c>
-      <c r="B72">
-        <v>2</v>
-      </c>
-      <c r="C72">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73">
-        <v>13030</v>
-      </c>
-      <c r="B73">
-        <v>3</v>
-      </c>
-      <c r="C73">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74">
-        <v>19687</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="C74">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75">
-        <v>20650</v>
-      </c>
-      <c r="B75">
-        <v>1</v>
-      </c>
-      <c r="C75">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76">
-        <v>20927</v>
-      </c>
-      <c r="B76">
-        <v>1</v>
-      </c>
-      <c r="C76">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77">
-        <v>21068</v>
-      </c>
-      <c r="B77">
-        <v>10</v>
-      </c>
-      <c r="C77">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78">
-        <v>22361</v>
-      </c>
-      <c r="B78">
-        <v>1</v>
-      </c>
-      <c r="C78">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79">
-        <v>24257</v>
-      </c>
-      <c r="B79">
-        <v>1</v>
-      </c>
-      <c r="C79">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80">
-        <v>24258</v>
-      </c>
-      <c r="B80">
-        <v>1</v>
-      </c>
-      <c r="C80">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81">
-        <v>24566</v>
-      </c>
-      <c r="B81">
-        <v>1</v>
-      </c>
-      <c r="C81">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82">
-        <v>24567</v>
-      </c>
-      <c r="B82">
-        <v>1</v>
-      </c>
-      <c r="C82">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83">
-        <v>25278</v>
-      </c>
-      <c r="B83">
-        <v>2</v>
-      </c>
-      <c r="C83">
-        <v>318</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,57 +396,57 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>267</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>42</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -457,40 +457,40 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>74</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10">
-        <v>349</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -501,100 +501,100 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>216</v>
+        <v>344</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>248</v>
+        <v>345</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="B15">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>40</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>361</v>
+        <v>434</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>73</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>362</v>
+        <v>435</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>65</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>378</v>
+        <v>566</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>87</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>434</v>
+        <v>616</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>92</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>435</v>
+        <v>624</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -605,98 +605,98 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>440</v>
+        <v>738</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>90</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>566</v>
+        <v>790</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>589</v>
+        <v>949</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C23">
-        <v>126</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>593</v>
+        <v>965</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C24">
-        <v>107</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>616</v>
+        <v>976</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>624</v>
+        <v>1007</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>63</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>738</v>
+        <v>1124</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>790</v>
+        <v>1309</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>949</v>
+        <v>1448</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -704,315 +704,315 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>965</v>
+        <v>1492</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>990</v>
+        <v>1654</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1007</v>
+        <v>1656</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32">
-        <v>129</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1124</v>
+        <v>1668</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>115</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1448</v>
+        <v>1728</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1490</v>
+        <v>2049</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1492</v>
+        <v>2188</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1654</v>
+        <v>2190</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1656</v>
+        <v>2216</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C38">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1668</v>
+        <v>2308</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C39">
-        <v>48</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1728</v>
+        <v>2327</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2188</v>
+        <v>2331</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2216</v>
+        <v>2419</v>
       </c>
       <c r="B42">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C42">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2327</v>
+        <v>2423</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C43">
-        <v>62</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2423</v>
+        <v>2436</v>
       </c>
       <c r="B44">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>87</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2424</v>
+        <v>2438</v>
       </c>
       <c r="B45">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>22</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2436</v>
+        <v>2934</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2934</v>
+        <v>2991</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2991</v>
+        <v>3016</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C48">
-        <v>68</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3016</v>
+        <v>3434</v>
       </c>
       <c r="B49">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>25</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3434</v>
+        <v>3475</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
       <c r="C50">
-        <v>86</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3475</v>
+        <v>3477</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3477</v>
+        <v>3495</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3495</v>
+        <v>3671</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3671</v>
+        <v>3894</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>11</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3894</v>
+        <v>3955</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>72</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3955</v>
+        <v>4019</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
       <c r="C56">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4019</v>
+        <v>4222</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C57">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4222</v>
+        <v>4223</v>
       </c>
       <c r="B58">
         <v>4</v>
@@ -1023,43 +1023,43 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4223</v>
+        <v>5111</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5080</v>
+        <v>5152</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5111</v>
+        <v>5153</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5152</v>
+        <v>5243</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62">
         <v>7</v>
@@ -1067,395 +1067,395 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5153</v>
+        <v>5453</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5243</v>
+        <v>5490</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5453</v>
+        <v>5493</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5490</v>
+        <v>5540</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>49</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5491</v>
+        <v>5541</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5493</v>
+        <v>5577</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5541</v>
+        <v>5585</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5577</v>
+        <v>5729</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5585</v>
+        <v>5730</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>115</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5729</v>
+        <v>5736</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5730</v>
+        <v>6098</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C73">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5733</v>
+        <v>6158</v>
       </c>
       <c r="B74">
         <v>2</v>
       </c>
       <c r="C74">
-        <v>25</v>
+        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5736</v>
+        <v>6496</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6097</v>
+        <v>6540</v>
       </c>
       <c r="B76">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C76">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6098</v>
+        <v>6627</v>
       </c>
       <c r="B77">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C77">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6158</v>
+        <v>6931</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>250</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6496</v>
+        <v>6936</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6540</v>
+        <v>7887</v>
       </c>
       <c r="B80">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C80">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>6627</v>
+        <v>8216</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6931</v>
+        <v>8356</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>114</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>6935</v>
+        <v>8648</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>142</v>
+        <v>173</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>6936</v>
+        <v>8649</v>
       </c>
       <c r="B84">
         <v>2</v>
       </c>
       <c r="C84">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>7520</v>
+        <v>8650</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>7886</v>
+        <v>8672</v>
       </c>
       <c r="B86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>68</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>7887</v>
+        <v>8675</v>
       </c>
       <c r="B87">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>66</v>
+        <v>139</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8216</v>
+        <v>8907</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C88">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8648</v>
+        <v>8915</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>173</v>
+        <v>78</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8649</v>
+        <v>8939</v>
       </c>
       <c r="B90">
         <v>2</v>
       </c>
       <c r="C90">
-        <v>116</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8672</v>
+        <v>9081</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C91">
-        <v>139</v>
+        <v>231</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8675</v>
+        <v>9357</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>139</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8915</v>
+        <v>9358</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>77</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8939</v>
+        <v>9529</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C94">
-        <v>77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9081</v>
+        <v>9530</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C95">
-        <v>231</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9358</v>
+        <v>10148</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9529</v>
+        <v>10149</v>
       </c>
       <c r="B97">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>458</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9530</v>
+        <v>10455</v>
       </c>
       <c r="B98">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C98">
         <v>7</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10148</v>
+        <v>10514</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C99">
         <v>7</v>
@@ -1474,230 +1474,230 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10455</v>
+        <v>10529</v>
       </c>
       <c r="B100">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10514</v>
+        <v>10530</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10529</v>
+        <v>10716</v>
       </c>
       <c r="B102">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C102">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10530</v>
+        <v>10717</v>
       </c>
       <c r="B103">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C103">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10716</v>
+        <v>10825</v>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>336</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10717</v>
+        <v>11151</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>909</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10825</v>
+        <v>11212</v>
       </c>
       <c r="B106">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C106">
-        <v>328</v>
+        <v>113</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>10993</v>
+        <v>11410</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C107">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11151</v>
+        <v>11738</v>
       </c>
       <c r="B108">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>894</v>
+        <v>29</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11212</v>
+        <v>11739</v>
       </c>
       <c r="B109">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>147</v>
+        <v>28</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11685</v>
+        <v>11767</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11737</v>
+        <v>11773</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11738</v>
+        <v>11836</v>
       </c>
       <c r="B112">
         <v>2</v>
       </c>
       <c r="C112">
-        <v>29</v>
+        <v>122</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11739</v>
+        <v>11837</v>
       </c>
       <c r="B113">
         <v>2</v>
       </c>
       <c r="C113">
-        <v>28</v>
+        <v>123</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11767</v>
+        <v>11844</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>130</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11773</v>
+        <v>11885</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>61</v>
+        <v>97</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11836</v>
+        <v>11920</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>161</v>
+        <v>74</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11837</v>
+        <v>12010</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C117">
-        <v>124</v>
+        <v>72</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11838</v>
+        <v>12040</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C118">
-        <v>122</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11844</v>
+        <v>12050</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C119">
-        <v>129</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11886</v>
+        <v>12294</v>
       </c>
       <c r="B120">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -1705,21 +1705,21 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12010</v>
+        <v>12526</v>
       </c>
       <c r="B121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12040</v>
+        <v>12535</v>
       </c>
       <c r="B122">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C122">
         <v>7</v>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12050</v>
+        <v>12538</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C123">
         <v>7</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12294</v>
+        <v>12539</v>
       </c>
       <c r="B124">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -1749,266 +1749,299 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12526</v>
+        <v>12764</v>
       </c>
       <c r="B125">
         <v>2</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>349</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12535</v>
+        <v>12791</v>
       </c>
       <c r="B126">
         <v>2</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>388</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12538</v>
+        <v>12923</v>
       </c>
       <c r="B127">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12539</v>
+        <v>12924</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12764</v>
+        <v>12925</v>
       </c>
       <c r="B129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C129">
-        <v>353</v>
+        <v>31</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12791</v>
+        <v>12979</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>388</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12923</v>
+        <v>13030</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>18</v>
+        <v>141</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>12924</v>
+        <v>13967</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>12925</v>
+        <v>19687</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>12979</v>
+        <v>19924</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C134">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>19687</v>
+        <v>20650</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>19924</v>
+        <v>20927</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>20650</v>
+        <v>20977</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>20927</v>
+        <v>21068</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C138">
-        <v>50</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21068</v>
+        <v>21454</v>
       </c>
       <c r="B139">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C139">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21454</v>
+        <v>21793</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>232</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>22326</v>
+        <v>22324</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>23380</v>
+        <v>22326</v>
       </c>
       <c r="B142">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>23992</v>
+        <v>22327</v>
       </c>
       <c r="B143">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C143">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>24256</v>
+        <v>23380</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C144">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>24257</v>
+        <v>23994</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C145">
-        <v>124</v>
+        <v>35</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>24566</v>
+        <v>24256</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>156</v>
+        <v>71</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>24567</v>
+        <v>24257</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>481</v>
+        <v>127</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>25278</v>
+        <v>24566</v>
       </c>
       <c r="B148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C148">
-        <v>138</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149">
+        <v>24567</v>
+      </c>
+      <c r="B149">
+        <v>1</v>
+      </c>
+      <c r="C149">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>25958</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>25960</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:C152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,147 +402,147 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>113</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>549</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>74</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>591</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>334</v>
+        <v>216</v>
       </c>
       <c r="B14">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>358</v>
+        <v>217</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -550,51 +550,51 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>413</v>
+        <v>305</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>40</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>566</v>
+        <v>345</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>738</v>
+        <v>378</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>788</v>
+        <v>416</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>790</v>
+        <v>417</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -605,32 +605,32 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>949</v>
+        <v>435</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>965</v>
+        <v>440</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>279</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>976</v>
+        <v>566</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>7</v>
@@ -638,76 +638,76 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>990</v>
+        <v>616</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1007</v>
+        <v>624</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>127</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1054</v>
+        <v>738</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>189</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1124</v>
+        <v>790</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>87</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1134</v>
+        <v>949</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1309</v>
+        <v>965</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>26</v>
+        <v>278</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1448</v>
+        <v>976</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -715,373 +715,373 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1455</v>
+        <v>990</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1492</v>
+        <v>1007</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>35</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1654</v>
+        <v>1134</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1656</v>
+        <v>1448</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1668</v>
+        <v>1490</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1728</v>
+        <v>1492</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2190</v>
+        <v>1504</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2216</v>
+        <v>1654</v>
       </c>
       <c r="B38">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2308</v>
+        <v>1656</v>
       </c>
       <c r="B39">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2327</v>
+        <v>1668</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2331</v>
+        <v>1728</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41">
-        <v>108</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2423</v>
+        <v>2188</v>
       </c>
       <c r="B42">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>90</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2436</v>
+        <v>2190</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2438</v>
+        <v>2216</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C44">
-        <v>315</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2492</v>
+        <v>2308</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2934</v>
+        <v>2327</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>14</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2990</v>
+        <v>2331</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>130</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2991</v>
+        <v>2419</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C48">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3016</v>
+        <v>2423</v>
       </c>
       <c r="B49">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C49">
-        <v>26</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3278</v>
+        <v>2424</v>
       </c>
       <c r="B50">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3434</v>
+        <v>2436</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C51">
-        <v>86</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3475</v>
+        <v>2438</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52">
-        <v>30</v>
+        <v>301</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3477</v>
+        <v>2934</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>50</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3495</v>
+        <v>2991</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
       <c r="C54">
-        <v>18</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3581</v>
+        <v>3016</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C55">
-        <v>103</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3598</v>
+        <v>3434</v>
       </c>
       <c r="B56">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3673</v>
+        <v>3475</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57">
-        <v>116</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3674</v>
+        <v>3495</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3894</v>
+        <v>3581</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59">
-        <v>109</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3955</v>
+        <v>3671</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4019</v>
+        <v>3894</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>45</v>
+        <v>109</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4223</v>
+        <v>3955</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5111</v>
+        <v>4019</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5152</v>
+        <v>4222</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C64">
         <v>7</v>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5153</v>
+        <v>4223</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C65">
         <v>7</v>
@@ -1100,29 +1100,29 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5243</v>
+        <v>5111</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5453</v>
+        <v>5152</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5493</v>
+        <v>5153</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -1133,252 +1133,252 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5540</v>
+        <v>5243</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>82</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5541</v>
+        <v>5453</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5577</v>
+        <v>5490</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5585</v>
+        <v>5540</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>120</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5730</v>
+        <v>5541</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6098</v>
+        <v>5577</v>
       </c>
       <c r="B74">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6158</v>
+        <v>5585</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6496</v>
+        <v>5730</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6540</v>
+        <v>5733</v>
       </c>
       <c r="B77">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6931</v>
+        <v>5736</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8104</v>
+        <v>6158</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>96</v>
+        <v>127</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8157</v>
+        <v>6496</v>
       </c>
       <c r="B80">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8648</v>
+        <v>6540</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C81">
-        <v>173</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8649</v>
+        <v>6931</v>
       </c>
       <c r="B82">
         <v>2</v>
       </c>
       <c r="C82">
-        <v>116</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8907</v>
+        <v>6935</v>
       </c>
       <c r="B83">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>7</v>
+        <v>261</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8923</v>
+        <v>7886</v>
       </c>
       <c r="B84">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C84">
-        <v>7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>9085</v>
+        <v>8089</v>
       </c>
       <c r="B85">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>88</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>9357</v>
+        <v>8157</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C86">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9358</v>
+        <v>8356</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9373</v>
+        <v>8649</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9529</v>
+        <v>8659</v>
       </c>
       <c r="B89">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9530</v>
+        <v>8673</v>
       </c>
       <c r="B90">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>7</v>
+        <v>137</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>10148</v>
+        <v>8907</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C91">
         <v>7</v>
@@ -1386,76 +1386,76 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>10149</v>
+        <v>8915</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>466</v>
+        <v>76</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10455</v>
+        <v>8939</v>
       </c>
       <c r="B93">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10514</v>
+        <v>9081</v>
       </c>
       <c r="B94">
         <v>3</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>231</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10524</v>
+        <v>9085</v>
       </c>
       <c r="B95">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C95">
-        <v>116</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>10529</v>
+        <v>9358</v>
       </c>
       <c r="B96">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10530</v>
+        <v>9529</v>
       </c>
       <c r="B97">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10716</v>
+        <v>9530</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C98">
         <v>7</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10717</v>
+        <v>10148</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C99">
         <v>7</v>
@@ -1474,153 +1474,153 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10825</v>
+        <v>10149</v>
       </c>
       <c r="B100">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C100">
-        <v>340</v>
+        <v>470</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11093</v>
+        <v>10455</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C101">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11151</v>
+        <v>10514</v>
       </c>
       <c r="B102">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C102">
-        <v>909</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11212</v>
+        <v>10529</v>
       </c>
       <c r="B103">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C103">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11410</v>
+        <v>10530</v>
       </c>
       <c r="B104">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11684</v>
+        <v>10716</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C105">
-        <v>254</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11737</v>
+        <v>10825</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C106">
-        <v>28</v>
+        <v>340</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11739</v>
+        <v>11093</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11773</v>
+        <v>11151</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>908</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11844</v>
+        <v>11212</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C109">
-        <v>130</v>
+        <v>115</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11885</v>
+        <v>11234</v>
       </c>
       <c r="B110">
         <v>2</v>
       </c>
       <c r="C110">
-        <v>97</v>
+        <v>115</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11920</v>
+        <v>11410</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C111">
-        <v>74</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>12010</v>
+        <v>11767</v>
       </c>
       <c r="B112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>12040</v>
+        <v>11773</v>
       </c>
       <c r="B113">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C113">
         <v>7</v>
@@ -1628,54 +1628,54 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>12048</v>
+        <v>11844</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>8</v>
+        <v>129</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12294</v>
+        <v>11885</v>
       </c>
       <c r="B115">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12304</v>
+        <v>11920</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12526</v>
+        <v>12010</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C117">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12535</v>
+        <v>12040</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C118">
         <v>7</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12538</v>
+        <v>12050</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12539</v>
+        <v>12294</v>
       </c>
       <c r="B120">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -1705,21 +1705,21 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12656</v>
+        <v>12526</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12923</v>
+        <v>12535</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122">
         <v>7</v>
@@ -1727,131 +1727,131 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12924</v>
+        <v>12538</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C123">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12925</v>
+        <v>12539</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>13030</v>
+        <v>12764</v>
       </c>
       <c r="B125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C125">
-        <v>141</v>
+        <v>351</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>13197</v>
+        <v>12791</v>
       </c>
       <c r="B126">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>13967</v>
+        <v>12923</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>18964</v>
+        <v>12924</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>19687</v>
+        <v>12925</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>19924</v>
+        <v>12979</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>19970</v>
+        <v>13030</v>
       </c>
       <c r="B131">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>8</v>
+        <v>141</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>19985</v>
+        <v>13928</v>
       </c>
       <c r="B132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C132">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>19997</v>
+        <v>19687</v>
       </c>
       <c r="B133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>20650</v>
+        <v>19924</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C134">
         <v>7</v>
@@ -1859,57 +1859,57 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>20927</v>
+        <v>20650</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>20977</v>
+        <v>20927</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>21068</v>
+        <v>20977</v>
       </c>
       <c r="B137">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>21454</v>
+        <v>21068</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21793</v>
+        <v>21454</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -1958,145 +1958,101 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>22364</v>
+        <v>23380</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23233</v>
+        <v>23992</v>
       </c>
       <c r="B145">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C145">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23238</v>
+        <v>23994</v>
       </c>
       <c r="B146">
         <v>29</v>
       </c>
       <c r="C146">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23380</v>
+        <v>24256</v>
       </c>
       <c r="B147">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23598</v>
+        <v>24257</v>
       </c>
       <c r="B148">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>35</v>
+        <v>86</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>23994</v>
+        <v>24566</v>
       </c>
       <c r="B149">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C149">
-        <v>35</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>24256</v>
+        <v>24567</v>
       </c>
       <c r="B150">
         <v>1</v>
       </c>
       <c r="C150">
-        <v>7</v>
+        <v>304</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>24257</v>
+        <v>25958</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C151">
-        <v>86</v>
+        <v>128</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>24669</v>
+        <v>25960</v>
       </c>
       <c r="B152">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C152">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153">
-        <v>24726</v>
-      </c>
-      <c r="B153">
-        <v>2</v>
-      </c>
-      <c r="C153">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154">
-        <v>25698</v>
-      </c>
-      <c r="B154">
-        <v>3</v>
-      </c>
-      <c r="C154">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155">
-        <v>25958</v>
-      </c>
-      <c r="B155">
-        <v>2</v>
-      </c>
-      <c r="C155">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156">
-        <v>25960</v>
-      </c>
-      <c r="B156">
-        <v>2</v>
-      </c>
-      <c r="C156">
-        <v>130</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,7 +402,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -418,13 +418,13 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>42</v>
+        <v>549</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -446,7 +446,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -457,7 +457,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -468,7 +468,7 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -479,18 +479,18 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>340</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -501,34 +501,34 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>591</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B14">
         <v>4</v>
@@ -539,62 +539,62 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>217</v>
+        <v>305</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>305</v>
+        <v>358</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>154</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>40</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>417</v>
+        <v>566</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -605,32 +605,32 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>435</v>
+        <v>616</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>440</v>
+        <v>624</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>125</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>566</v>
+        <v>738</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
         <v>7</v>
@@ -638,32 +638,32 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>616</v>
+        <v>788</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>624</v>
+        <v>790</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>738</v>
+        <v>949</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C26">
         <v>7</v>
@@ -671,21 +671,21 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>790</v>
+        <v>965</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -693,21 +693,21 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>965</v>
+        <v>1007</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>278</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>976</v>
+        <v>1134</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -715,106 +715,106 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>990</v>
+        <v>1309</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1007</v>
+        <v>1448</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>128</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1134</v>
+        <v>1490</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1448</v>
+        <v>1492</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1490</v>
+        <v>1654</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1492</v>
+        <v>1656</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1504</v>
+        <v>1668</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>106</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1654</v>
+        <v>1728</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1656</v>
+        <v>2188</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1668</v>
+        <v>2190</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -825,10 +825,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1728</v>
+        <v>2216</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C41">
         <v>7</v>
@@ -836,241 +836,241 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2188</v>
+        <v>2308</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C42">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2190</v>
+        <v>2327</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2216</v>
+        <v>2331</v>
       </c>
       <c r="B44">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2308</v>
+        <v>2419</v>
       </c>
       <c r="B45">
         <v>29</v>
       </c>
       <c r="C45">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2327</v>
+        <v>2422</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C46">
-        <v>62</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2331</v>
+        <v>2423</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C47">
-        <v>57</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2419</v>
+        <v>2424</v>
       </c>
       <c r="B48">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="C48">
-        <v>34</v>
+        <v>158</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2423</v>
+        <v>2436</v>
       </c>
       <c r="B49">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="C49">
-        <v>90</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2424</v>
+        <v>2991</v>
       </c>
       <c r="B50">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2436</v>
+        <v>3016</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="C51">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2438</v>
+        <v>3278</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C52">
-        <v>301</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2934</v>
+        <v>3434</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2991</v>
+        <v>3475</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>68</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3016</v>
+        <v>3495</v>
       </c>
       <c r="B55">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3434</v>
+        <v>3581</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3475</v>
+        <v>3671</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3495</v>
+        <v>3674</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3581</v>
+        <v>3894</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3671</v>
+        <v>3955</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3894</v>
+        <v>4019</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>109</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3955</v>
+        <v>4222</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C62">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>4019</v>
+        <v>4223</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C63">
         <v>7</v>
@@ -1078,21 +1078,21 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>4222</v>
+        <v>5111</v>
       </c>
       <c r="B64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>4223</v>
+        <v>5152</v>
       </c>
       <c r="B65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C65">
         <v>7</v>
@@ -1100,21 +1100,21 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5111</v>
+        <v>5153</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5152</v>
+        <v>5243</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67">
         <v>7</v>
@@ -1122,65 +1122,65 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5153</v>
+        <v>5453</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5243</v>
+        <v>5540</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5453</v>
+        <v>5541</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5490</v>
+        <v>5577</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5540</v>
+        <v>5585</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>82</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5541</v>
+        <v>5730</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
         <v>7</v>
@@ -1188,189 +1188,189 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5577</v>
+        <v>5733</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5585</v>
+        <v>5736</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>121</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5730</v>
+        <v>6158</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76">
-        <v>29</v>
+        <v>127</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5733</v>
+        <v>6496</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5736</v>
+        <v>6540</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C78">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6158</v>
+        <v>6628</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>127</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6496</v>
+        <v>6931</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>6540</v>
+        <v>6935</v>
       </c>
       <c r="B81">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6931</v>
+        <v>7886</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C82">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>6935</v>
+        <v>8089</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>261</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>7886</v>
+        <v>8157</v>
       </c>
       <c r="B84">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C84">
-        <v>68</v>
+        <v>88</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8089</v>
+        <v>8216</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8157</v>
+        <v>8356</v>
       </c>
       <c r="B86">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>88</v>
+        <v>43</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8356</v>
+        <v>8649</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>43</v>
+        <v>115</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8649</v>
+        <v>8659</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8659</v>
+        <v>8675</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>76</v>
+        <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8673</v>
+        <v>8688</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C90">
-        <v>137</v>
+        <v>178</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1386,13 +1386,13 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8915</v>
+        <v>8923</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C92">
-        <v>76</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1403,29 +1403,29 @@
         <v>2</v>
       </c>
       <c r="C93">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9081</v>
+        <v>9085</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C94">
-        <v>231</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9085</v>
+        <v>9357</v>
       </c>
       <c r="B95">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>88</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1463,32 +1463,32 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10148</v>
+        <v>10149</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>474</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10149</v>
+        <v>10455</v>
       </c>
       <c r="B100">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C100">
-        <v>470</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10455</v>
+        <v>10514</v>
       </c>
       <c r="B101">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C101">
         <v>7</v>
@@ -1496,13 +1496,13 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10514</v>
+        <v>10524</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1557,7 +1557,7 @@
         <v>1</v>
       </c>
       <c r="C107">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1579,7 +1579,7 @@
         <v>4</v>
       </c>
       <c r="C109">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1590,7 +1590,7 @@
         <v>2</v>
       </c>
       <c r="C110">
-        <v>115</v>
+        <v>87</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -1606,46 +1606,46 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11767</v>
+        <v>11737</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>79</v>
+        <v>28</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11773</v>
+        <v>11844</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11844</v>
+        <v>11885</v>
       </c>
       <c r="B114">
         <v>2</v>
       </c>
       <c r="C114">
-        <v>129</v>
+        <v>93</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11885</v>
+        <v>11886</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -1656,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="C116">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -1667,7 +1667,7 @@
         <v>3</v>
       </c>
       <c r="C117">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12526</v>
+        <v>12513</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121">
         <v>7</v>
@@ -1755,7 +1755,7 @@
         <v>2</v>
       </c>
       <c r="C125">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -1766,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="C126">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -1799,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="C129">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -1821,7 +1821,7 @@
         <v>3</v>
       </c>
       <c r="C131">
-        <v>141</v>
+        <v>70</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -1837,32 +1837,32 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>19687</v>
+        <v>19685</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>19924</v>
+        <v>19687</v>
       </c>
       <c r="B134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>20650</v>
+        <v>19924</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135">
         <v>7</v>
@@ -1870,18 +1870,18 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>20927</v>
+        <v>19997</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>20977</v>
+        <v>20650</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -1892,21 +1892,21 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>21068</v>
+        <v>20927</v>
       </c>
       <c r="B138">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21454</v>
+        <v>20977</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C139">
         <v>7</v>
@@ -1914,21 +1914,21 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>22324</v>
+        <v>21068</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>22325</v>
+        <v>21454</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141">
         <v>7</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>22326</v>
+        <v>22324</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>22327</v>
+        <v>22325</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -1958,101 +1958,167 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>23380</v>
+        <v>22326</v>
       </c>
       <c r="B144">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C144">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23992</v>
+        <v>22327</v>
       </c>
       <c r="B145">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C145">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23994</v>
+        <v>23233</v>
       </c>
       <c r="B146">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C146">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>24256</v>
+        <v>23238</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>24257</v>
+        <v>23380</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C148">
-        <v>86</v>
+        <v>15</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>24566</v>
+        <v>23994</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C149">
-        <v>150</v>
+        <v>35</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>24567</v>
+        <v>24256</v>
       </c>
       <c r="B150">
         <v>1</v>
       </c>
       <c r="C150">
-        <v>304</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>25958</v>
+        <v>24257</v>
       </c>
       <c r="B151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C151">
-        <v>128</v>
+        <v>86</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
+        <v>24566</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+      <c r="C152">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>24567</v>
+      </c>
+      <c r="B153">
+        <v>1</v>
+      </c>
+      <c r="C153">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>24669</v>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+      <c r="C154">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155">
+        <v>24726</v>
+      </c>
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156">
+        <v>25278</v>
+      </c>
+      <c r="B156">
+        <v>2</v>
+      </c>
+      <c r="C156">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157">
+        <v>25958</v>
+      </c>
+      <c r="B157">
+        <v>2</v>
+      </c>
+      <c r="C157">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158">
         <v>25960</v>
       </c>
-      <c r="B152">
-        <v>2</v>
-      </c>
-      <c r="C152">
-        <v>173</v>
+      <c r="B158">
+        <v>2</v>
+      </c>
+      <c r="C158">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C158"/>
+  <dimension ref="A1:C154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,90 +396,90 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>54</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>265</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>549</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>41</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>71</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -490,7 +490,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -501,23 +501,23 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -528,7 +528,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B14">
         <v>4</v>
@@ -539,106 +539,106 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>305</v>
+        <v>248</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>358</v>
+        <v>305</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>378</v>
+        <v>308</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>115</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>435</v>
+        <v>345</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>94</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>440</v>
+        <v>378</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>95</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>566</v>
+        <v>411</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>616</v>
+        <v>435</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>47</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>624</v>
+        <v>440</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>48</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>738</v>
+        <v>523</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>788</v>
+        <v>566</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -649,43 +649,43 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>790</v>
+        <v>593</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>949</v>
+        <v>616</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>965</v>
+        <v>624</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>278</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>976</v>
+        <v>738</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -693,21 +693,21 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1007</v>
+        <v>790</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>128</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1134</v>
+        <v>949</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -715,131 +715,131 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1309</v>
+        <v>950</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1448</v>
+        <v>965</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1490</v>
+        <v>976</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1492</v>
+        <v>1007</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>17</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1654</v>
+        <v>1134</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1656</v>
+        <v>1448</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1668</v>
+        <v>1490</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1728</v>
+        <v>1492</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2188</v>
+        <v>1654</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2190</v>
+        <v>1656</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2216</v>
+        <v>1668</v>
       </c>
       <c r="B41">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2308</v>
+        <v>1728</v>
       </c>
       <c r="B42">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C42">
         <v>7</v>
@@ -847,46 +847,46 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2327</v>
+        <v>2190</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2331</v>
+        <v>2265</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C44">
-        <v>60</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2419</v>
+        <v>2327</v>
       </c>
       <c r="B45">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>34</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2422</v>
+        <v>2419</v>
       </c>
       <c r="B46">
         <v>29</v>
       </c>
       <c r="C46">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -897,7 +897,7 @@
         <v>80</v>
       </c>
       <c r="C47">
-        <v>114</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -908,7 +908,7 @@
         <v>80</v>
       </c>
       <c r="C48">
-        <v>158</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -919,37 +919,37 @@
         <v>4</v>
       </c>
       <c r="C49">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2991</v>
+        <v>2934</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>68</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3016</v>
+        <v>2991</v>
       </c>
       <c r="B51">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3278</v>
+        <v>3016</v>
       </c>
       <c r="B52">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="C52">
         <v>7</v>
@@ -963,18 +963,18 @@
         <v>2</v>
       </c>
       <c r="C53">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3475</v>
+        <v>3477</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -985,15 +985,15 @@
         <v>3</v>
       </c>
       <c r="C55">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3581</v>
+        <v>3671</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56">
         <v>7</v>
@@ -1001,65 +1001,65 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3671</v>
+        <v>3894</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3674</v>
+        <v>3955</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3894</v>
+        <v>4222</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C59">
-        <v>109</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3955</v>
+        <v>4223</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C60">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4019</v>
+        <v>5111</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4222</v>
+        <v>5152</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C62">
         <v>7</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>4223</v>
+        <v>5153</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C63">
         <v>7</v>
@@ -1078,43 +1078,43 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5111</v>
+        <v>5243</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5152</v>
+        <v>5453</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5153</v>
+        <v>5540</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5243</v>
+        <v>5541</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C67">
         <v>7</v>
@@ -1122,43 +1122,43 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5453</v>
+        <v>5577</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5540</v>
+        <v>5585</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>82</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5541</v>
+        <v>5729</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5577</v>
+        <v>5730</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71">
         <v>7</v>
@@ -1166,282 +1166,282 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5585</v>
+        <v>5733</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5730</v>
+        <v>5736</v>
       </c>
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5733</v>
+        <v>6098</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C74">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5736</v>
+        <v>6158</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>24</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6158</v>
+        <v>6540</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C76">
-        <v>127</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6496</v>
+        <v>6931</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>19</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6540</v>
+        <v>6936</v>
       </c>
       <c r="B78">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6628</v>
+        <v>7204</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6931</v>
+        <v>7886</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C80">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>6935</v>
+        <v>8216</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7886</v>
+        <v>8648</v>
       </c>
       <c r="B82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>68</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8089</v>
+        <v>8649</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>33</v>
+        <v>123</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8157</v>
+        <v>8650</v>
       </c>
       <c r="B84">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>88</v>
+        <v>184</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8216</v>
+        <v>8675</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>42</v>
+        <v>145</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8356</v>
+        <v>8676</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>43</v>
+        <v>147</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8649</v>
+        <v>8907</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C87">
-        <v>115</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8659</v>
+        <v>8915</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>114</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8675</v>
+        <v>8939</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>136</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8688</v>
+        <v>9070</v>
       </c>
       <c r="B90">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>178</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8907</v>
+        <v>9208</v>
       </c>
       <c r="B91">
         <v>29</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8923</v>
+        <v>9209</v>
       </c>
       <c r="B92">
         <v>29</v>
       </c>
       <c r="C92">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8939</v>
+        <v>9239</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C93">
-        <v>75</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9085</v>
+        <v>9507</v>
       </c>
       <c r="B94">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C94">
-        <v>88</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9357</v>
+        <v>9529</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9358</v>
+        <v>9530</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C96">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9529</v>
+        <v>10148</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -1452,32 +1452,32 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9530</v>
+        <v>10149</v>
       </c>
       <c r="B98">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10149</v>
+        <v>10455</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C99">
-        <v>474</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10455</v>
+        <v>10514</v>
       </c>
       <c r="B100">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C100">
         <v>7</v>
@@ -1485,68 +1485,68 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10514</v>
+        <v>10529</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10524</v>
+        <v>10530</v>
       </c>
       <c r="B102">
         <v>80</v>
       </c>
       <c r="C102">
-        <v>116</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10529</v>
+        <v>10716</v>
       </c>
       <c r="B103">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C103">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10530</v>
+        <v>10717</v>
       </c>
       <c r="B104">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C104">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10716</v>
+        <v>10825</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10825</v>
+        <v>10993</v>
       </c>
       <c r="B106">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>340</v>
+        <v>28</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1568,7 +1568,7 @@
         <v>11</v>
       </c>
       <c r="C108">
-        <v>908</v>
+        <v>967</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1579,103 +1579,103 @@
         <v>4</v>
       </c>
       <c r="C109">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11234</v>
+        <v>11410</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C110">
-        <v>87</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11410</v>
+        <v>11738</v>
       </c>
       <c r="B111">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11737</v>
+        <v>11739</v>
       </c>
       <c r="B112">
         <v>2</v>
       </c>
       <c r="C112">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11844</v>
+        <v>11773</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>128</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11885</v>
+        <v>11844</v>
       </c>
       <c r="B114">
         <v>2</v>
       </c>
       <c r="C114">
-        <v>93</v>
+        <v>141</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11886</v>
+        <v>11885</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11920</v>
+        <v>11886</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>102</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12010</v>
+        <v>11920</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>76</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12040</v>
+        <v>12010</v>
       </c>
       <c r="B118">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C118">
         <v>7</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12050</v>
+        <v>12040</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12294</v>
+        <v>12050</v>
       </c>
       <c r="B120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12513</v>
+        <v>12294</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C121">
         <v>7</v>
@@ -1722,7 +1722,7 @@
         <v>2</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -1738,13 +1738,13 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12539</v>
+        <v>12721</v>
       </c>
       <c r="B124">
         <v>2</v>
       </c>
       <c r="C124">
-        <v>7</v>
+        <v>144</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -1755,7 +1755,7 @@
         <v>2</v>
       </c>
       <c r="C125">
-        <v>353</v>
+        <v>386</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -1766,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="C126">
-        <v>396</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -1782,32 +1782,32 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12924</v>
+        <v>12925</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12925</v>
+        <v>12979</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12979</v>
+        <v>13257</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C130">
         <v>20</v>
@@ -1815,98 +1815,98 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13030</v>
+        <v>13258</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C131">
-        <v>70</v>
+        <v>360</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13928</v>
+        <v>13259</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C132">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>19685</v>
+        <v>13260</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C133">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>19687</v>
+        <v>13269</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C134">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>19924</v>
+        <v>13272</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>19997</v>
+        <v>13964</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>20650</v>
+        <v>13965</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>20927</v>
+        <v>13967</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>20977</v>
+        <v>19924</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139">
         <v>7</v>
@@ -1914,43 +1914,43 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21068</v>
+        <v>20650</v>
       </c>
       <c r="B140">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>10</v>
+        <v>116</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21454</v>
+        <v>20927</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>22324</v>
+        <v>21068</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C142">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>22325</v>
+        <v>21454</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C143">
         <v>7</v>
@@ -1958,18 +1958,18 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>22326</v>
+        <v>21793</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>122</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22327</v>
+        <v>22324</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -1980,24 +1980,24 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23233</v>
+        <v>22326</v>
       </c>
       <c r="B146">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23238</v>
+        <v>22327</v>
       </c>
       <c r="B147">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2008,23 +2008,23 @@
         <v>29</v>
       </c>
       <c r="C148">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>23994</v>
+        <v>23992</v>
       </c>
       <c r="B149">
         <v>29</v>
       </c>
       <c r="C149">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>24256</v>
+        <v>24566</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2035,90 +2035,46 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>24257</v>
+        <v>24567</v>
       </c>
       <c r="B151">
         <v>1</v>
       </c>
       <c r="C151">
-        <v>86</v>
+        <v>173</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>24566</v>
+        <v>24669</v>
       </c>
       <c r="B152">
         <v>1</v>
       </c>
       <c r="C152">
-        <v>152</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>24567</v>
+        <v>25278</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C153">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>24669</v>
+        <v>25960</v>
       </c>
       <c r="B154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C154">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155">
-        <v>24726</v>
-      </c>
-      <c r="B155">
-        <v>2</v>
-      </c>
-      <c r="C155">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156">
-        <v>25278</v>
-      </c>
-      <c r="B156">
-        <v>2</v>
-      </c>
-      <c r="C156">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157">
-        <v>25958</v>
-      </c>
-      <c r="B157">
-        <v>2</v>
-      </c>
-      <c r="C157">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158">
-        <v>25960</v>
-      </c>
-      <c r="B158">
-        <v>2</v>
-      </c>
-      <c r="C158">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
@@ -418,18 +418,18 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -440,24 +440,24 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -473,65 +473,65 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>480</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>164</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>216</v>
+        <v>308</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>217</v>
+        <v>358</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>7</v>
@@ -539,109 +539,109 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>248</v>
+        <v>378</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>305</v>
+        <v>411</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>308</v>
+        <v>413</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>345</v>
+        <v>440</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>219</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>378</v>
+        <v>566</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>123</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>411</v>
+        <v>593</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>54</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>435</v>
+        <v>624</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>440</v>
+        <v>738</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>102</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>523</v>
+        <v>790</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>566</v>
+        <v>949</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C24">
         <v>7</v>
@@ -649,54 +649,54 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>593</v>
+        <v>950</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>115</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>616</v>
+        <v>965</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>51</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>624</v>
+        <v>976</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>738</v>
+        <v>1007</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>790</v>
+        <v>1134</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -704,10 +704,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>949</v>
+        <v>1448</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -715,62 +715,62 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>950</v>
+        <v>1490</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>965</v>
+        <v>1492</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>297</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>976</v>
+        <v>1654</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1007</v>
+        <v>1656</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34">
-        <v>139</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1134</v>
+        <v>1668</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1448</v>
+        <v>1728</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -781,76 +781,76 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1490</v>
+        <v>2188</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1492</v>
+        <v>2190</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1654</v>
+        <v>2265</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1656</v>
+        <v>2327</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40">
-        <v>46</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1668</v>
+        <v>2419</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C41">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1728</v>
+        <v>2423</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2190</v>
+        <v>2436</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>7</v>
@@ -858,106 +858,106 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2265</v>
+        <v>2934</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2327</v>
+        <v>2991</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>66</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2419</v>
+        <v>3016</v>
       </c>
       <c r="B46">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="C46">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2423</v>
+        <v>3434</v>
       </c>
       <c r="B47">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>95</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2424</v>
+        <v>3495</v>
       </c>
       <c r="B48">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>86</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2436</v>
+        <v>3581</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>63</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2934</v>
+        <v>3671</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2991</v>
+        <v>3674</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>96</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3016</v>
+        <v>3894</v>
       </c>
       <c r="B52">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3434</v>
+        <v>3955</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -968,65 +968,65 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3477</v>
+        <v>4222</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3495</v>
+        <v>4223</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3671</v>
+        <v>5111</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3894</v>
+        <v>5152</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3955</v>
+        <v>5153</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4222</v>
+        <v>5243</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59">
         <v>7</v>
@@ -1034,32 +1034,32 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4223</v>
+        <v>5453</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5111</v>
+        <v>5540</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
       <c r="C61">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5152</v>
+        <v>5541</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
         <v>7</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5153</v>
+        <v>5577</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63">
         <v>7</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5243</v>
+        <v>5585</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -1089,51 +1089,51 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5453</v>
+        <v>5736</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5540</v>
+        <v>6098</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C66">
-        <v>89</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5541</v>
+        <v>6158</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5577</v>
+        <v>6540</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5585</v>
+        <v>6628</v>
       </c>
       <c r="B69">
         <v>3</v>
@@ -1144,285 +1144,285 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5729</v>
+        <v>6931</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5730</v>
+        <v>6935</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>281</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5733</v>
+        <v>7204</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5736</v>
+        <v>8157</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C73">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6098</v>
+        <v>8216</v>
       </c>
       <c r="B74">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6158</v>
+        <v>8648</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>136</v>
+        <v>184</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6540</v>
+        <v>8649</v>
       </c>
       <c r="B76">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>39</v>
+        <v>92</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6931</v>
+        <v>8650</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77">
-        <v>52</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6936</v>
+        <v>8675</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>13</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>7204</v>
+        <v>8853</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7886</v>
+        <v>8907</v>
       </c>
       <c r="B80">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C80">
-        <v>72</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8216</v>
+        <v>8923</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C81">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8648</v>
+        <v>8939</v>
       </c>
       <c r="B82">
         <v>2</v>
       </c>
       <c r="C82">
-        <v>184</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8649</v>
+        <v>9085</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C83">
-        <v>123</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8650</v>
+        <v>9208</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C84">
-        <v>184</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8675</v>
+        <v>9209</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C85">
-        <v>145</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8676</v>
+        <v>9239</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C86">
-        <v>147</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8907</v>
+        <v>9357</v>
       </c>
       <c r="B87">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8915</v>
+        <v>9507</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>80</v>
+        <v>103</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8939</v>
+        <v>9529</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C89">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9070</v>
+        <v>9530</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C90">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9208</v>
+        <v>9531</v>
       </c>
       <c r="B91">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C91">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9209</v>
+        <v>10147</v>
       </c>
       <c r="B92">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>9239</v>
+        <v>10148</v>
       </c>
       <c r="B93">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9507</v>
+        <v>10149</v>
       </c>
       <c r="B94">
         <v>3</v>
       </c>
       <c r="C94">
-        <v>103</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9529</v>
+        <v>10455</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C95">
         <v>7</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9530</v>
+        <v>10514</v>
       </c>
       <c r="B96">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C96">
         <v>7</v>
@@ -1441,32 +1441,32 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10148</v>
+        <v>10524</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>164</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10149</v>
+        <v>10530</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C98">
-        <v>21</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10455</v>
+        <v>10716</v>
       </c>
       <c r="B99">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C99">
         <v>7</v>
@@ -1474,43 +1474,43 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10514</v>
+        <v>10717</v>
       </c>
       <c r="B100">
         <v>3</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10529</v>
+        <v>10825</v>
       </c>
       <c r="B101">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="C101">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10530</v>
+        <v>10993</v>
       </c>
       <c r="B102">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>75</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10716</v>
+        <v>11093</v>
       </c>
       <c r="B103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C103">
         <v>7</v>
@@ -1518,84 +1518,84 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10717</v>
+        <v>11151</v>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C104">
-        <v>64</v>
+        <v>967</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10825</v>
+        <v>11212</v>
       </c>
       <c r="B105">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C105">
-        <v>10</v>
+        <v>128</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10993</v>
+        <v>11410</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C106">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11093</v>
+        <v>11681</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>271</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11151</v>
+        <v>11685</v>
       </c>
       <c r="B108">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>967</v>
+        <v>271</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11212</v>
+        <v>11737</v>
       </c>
       <c r="B109">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11410</v>
+        <v>11738</v>
       </c>
       <c r="B110">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11738</v>
+        <v>11739</v>
       </c>
       <c r="B111">
         <v>2</v>
@@ -1606,24 +1606,24 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11739</v>
+        <v>11773</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11773</v>
+        <v>11837</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>129</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -1634,7 +1634,7 @@
         <v>2</v>
       </c>
       <c r="C114">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -1645,7 +1645,7 @@
         <v>2</v>
       </c>
       <c r="C115">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -1656,7 +1656,7 @@
         <v>2</v>
       </c>
       <c r="C116">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -1678,7 +1678,7 @@
         <v>3</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -1716,57 +1716,57 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12535</v>
+        <v>12513</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C122">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12538</v>
+        <v>12535</v>
       </c>
       <c r="B123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C123">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12721</v>
+        <v>12538</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C124">
-        <v>144</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12764</v>
+        <v>12721</v>
       </c>
       <c r="B125">
         <v>2</v>
       </c>
       <c r="C125">
-        <v>386</v>
+        <v>144</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12791</v>
+        <v>12764</v>
       </c>
       <c r="B126">
         <v>2</v>
       </c>
       <c r="C126">
-        <v>8</v>
+        <v>388</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -1782,24 +1782,24 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12925</v>
+        <v>12979</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12979</v>
+        <v>13030</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>21</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -1832,7 +1832,7 @@
         <v>25</v>
       </c>
       <c r="C132">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -1843,7 +1843,7 @@
         <v>29</v>
       </c>
       <c r="C133">
-        <v>72</v>
+        <v>37</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -1854,26 +1854,26 @@
         <v>29</v>
       </c>
       <c r="C134">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13272</v>
+        <v>13271</v>
       </c>
       <c r="B135">
         <v>29</v>
       </c>
       <c r="C135">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13964</v>
+        <v>13272</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C136">
         <v>52</v>
@@ -1881,90 +1881,90 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13965</v>
+        <v>13276</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C137">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>13967</v>
+        <v>13964</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>19924</v>
+        <v>13967</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>20650</v>
+        <v>19924</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>116</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>20927</v>
+        <v>20650</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>40</v>
+        <v>116</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21068</v>
+        <v>20927</v>
       </c>
       <c r="B142">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21454</v>
+        <v>21068</v>
       </c>
       <c r="B143">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>21793</v>
+        <v>21454</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C144">
-        <v>122</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -1986,7 +1986,7 @@
         <v>1</v>
       </c>
       <c r="C146">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2002,13 +2002,13 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23380</v>
+        <v>23233</v>
       </c>
       <c r="B148">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C148">
-        <v>16</v>
+        <v>48</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2024,57 +2024,57 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>24566</v>
+        <v>23994</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C150">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>24567</v>
+        <v>24566</v>
       </c>
       <c r="B151">
         <v>1</v>
       </c>
       <c r="C151">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>24669</v>
+        <v>24567</v>
       </c>
       <c r="B152">
         <v>1</v>
       </c>
       <c r="C152">
-        <v>7</v>
+        <v>176</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>25278</v>
+        <v>24669</v>
       </c>
       <c r="B153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C153">
-        <v>145</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>25960</v>
+        <v>24726</v>
       </c>
       <c r="B154">
         <v>2</v>
       </c>
       <c r="C154">
-        <v>137</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,51 +396,51 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>292</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -451,13 +451,13 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -468,23 +468,23 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -495,7 +495,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -506,84 +506,84 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>305</v>
+        <v>248</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>76</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>358</v>
+        <v>308</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>92</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>411</v>
+        <v>362</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>413</v>
+        <v>378</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>566</v>
+        <v>417</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -594,32 +594,32 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>593</v>
+        <v>435</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>115</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>624</v>
+        <v>440</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>52</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>738</v>
+        <v>566</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
         <v>7</v>
@@ -627,54 +627,54 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>790</v>
+        <v>589</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>949</v>
+        <v>593</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>950</v>
+        <v>616</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>965</v>
+        <v>624</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>296</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>976</v>
+        <v>738</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27">
         <v>7</v>
@@ -682,21 +682,21 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1007</v>
+        <v>790</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>139</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1134</v>
+        <v>949</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -704,98 +704,98 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1448</v>
+        <v>950</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1490</v>
+        <v>965</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C31">
-        <v>26</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1492</v>
+        <v>976</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1654</v>
+        <v>1309</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1656</v>
+        <v>1448</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1668</v>
+        <v>1490</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1728</v>
+        <v>1492</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2188</v>
+        <v>1654</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2190</v>
+        <v>1655</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38">
         <v>7</v>
@@ -803,87 +803,87 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2265</v>
+        <v>1656</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2327</v>
+        <v>1668</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>66</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2419</v>
+        <v>1728</v>
       </c>
       <c r="B41">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2423</v>
+        <v>2190</v>
       </c>
       <c r="B42">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2436</v>
+        <v>2327</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2934</v>
+        <v>2419</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C44">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2991</v>
+        <v>2423</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C45">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>3016</v>
+        <v>2436</v>
       </c>
       <c r="B46">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="C46">
         <v>7</v>
@@ -891,57 +891,57 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3434</v>
+        <v>2438</v>
       </c>
       <c r="B47">
         <v>2</v>
       </c>
       <c r="C47">
-        <v>46</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3495</v>
+        <v>2934</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3581</v>
+        <v>2991</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3671</v>
+        <v>3434</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
       <c r="C50">
-        <v>8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3674</v>
+        <v>3495</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>126</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -952,7 +952,7 @@
         <v>1</v>
       </c>
       <c r="C52">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -963,23 +963,23 @@
         <v>2</v>
       </c>
       <c r="C53">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>4222</v>
+        <v>4019</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>4223</v>
+        <v>4222</v>
       </c>
       <c r="B55">
         <v>4</v>
@@ -990,29 +990,29 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>5111</v>
+        <v>4223</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>5152</v>
+        <v>5111</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5153</v>
+        <v>5152</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5243</v>
+        <v>5153</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59">
         <v>7</v>
@@ -1034,373 +1034,373 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5453</v>
+        <v>5243</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5540</v>
+        <v>5453</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
       <c r="C61">
-        <v>90</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5541</v>
+        <v>5491</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5577</v>
+        <v>5493</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5585</v>
+        <v>5540</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5736</v>
+        <v>5541</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>6098</v>
+        <v>5577</v>
       </c>
       <c r="B66">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C66">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>6158</v>
+        <v>5585</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>6540</v>
+        <v>5730</v>
       </c>
       <c r="B68">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>6628</v>
+        <v>5736</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>6931</v>
+        <v>6097</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C70">
-        <v>52</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>6935</v>
+        <v>6098</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C71">
-        <v>281</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>7204</v>
+        <v>6158</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>20</v>
+        <v>309</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>8157</v>
+        <v>6540</v>
       </c>
       <c r="B73">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C73">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>8216</v>
+        <v>6627</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>8648</v>
+        <v>6931</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>184</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>8649</v>
+        <v>6935</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76">
-        <v>92</v>
+        <v>281</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8650</v>
+        <v>6936</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8675</v>
+        <v>7004</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>146</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8853</v>
+        <v>7886</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C79">
-        <v>9</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8907</v>
+        <v>8648</v>
       </c>
       <c r="B80">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>29</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8923</v>
+        <v>8649</v>
       </c>
       <c r="B81">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>29</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8939</v>
+        <v>8650</v>
       </c>
       <c r="B82">
         <v>2</v>
       </c>
       <c r="C82">
-        <v>81</v>
+        <v>123</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>9085</v>
+        <v>8672</v>
       </c>
       <c r="B83">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>94</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>9208</v>
+        <v>8853</v>
       </c>
       <c r="B84">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>33</v>
+        <v>284</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>9209</v>
+        <v>8907</v>
       </c>
       <c r="B85">
         <v>29</v>
       </c>
       <c r="C85">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>9239</v>
+        <v>8915</v>
       </c>
       <c r="B86">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>15</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9357</v>
+        <v>8939</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>13</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9507</v>
+        <v>9208</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C88">
-        <v>103</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9529</v>
+        <v>9209</v>
       </c>
       <c r="B89">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C89">
-        <v>7</v>
+        <v>200</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9530</v>
+        <v>9239</v>
       </c>
       <c r="B90">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C90">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9531</v>
+        <v>9358</v>
       </c>
       <c r="B91">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>10147</v>
+        <v>9529</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10148</v>
+        <v>9530</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -1408,32 +1408,32 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10149</v>
+        <v>10148</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10455</v>
+        <v>10149</v>
       </c>
       <c r="B95">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>10514</v>
+        <v>10455</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C96">
         <v>7</v>
@@ -1441,101 +1441,101 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10524</v>
+        <v>10514</v>
       </c>
       <c r="B97">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>164</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10530</v>
+        <v>10529</v>
       </c>
       <c r="B98">
         <v>80</v>
       </c>
       <c r="C98">
-        <v>75</v>
+        <v>109</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10716</v>
+        <v>10530</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10717</v>
+        <v>10716</v>
       </c>
       <c r="B100">
         <v>3</v>
       </c>
       <c r="C100">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10825</v>
+        <v>10717</v>
       </c>
       <c r="B101">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10993</v>
+        <v>10825</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C102">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11093</v>
+        <v>11151</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>967</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11151</v>
+        <v>11212</v>
       </c>
       <c r="B104">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C104">
-        <v>967</v>
+        <v>129</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11212</v>
+        <v>11396</v>
       </c>
       <c r="B105">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>128</v>
+        <v>46</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1551,7 +1551,7 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11681</v>
+        <v>11685</v>
       </c>
       <c r="B107">
         <v>2</v>
@@ -1562,84 +1562,84 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11685</v>
+        <v>11738</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108">
-        <v>271</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11737</v>
+        <v>11773</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11738</v>
+        <v>11835</v>
       </c>
       <c r="B110">
         <v>2</v>
       </c>
       <c r="C110">
-        <v>31</v>
+        <v>128</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11739</v>
+        <v>11837</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11773</v>
+        <v>11838</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>131</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11837</v>
+        <v>11844</v>
       </c>
       <c r="B113">
         <v>2</v>
       </c>
       <c r="C113">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11844</v>
+        <v>11885</v>
       </c>
       <c r="B114">
         <v>2</v>
       </c>
       <c r="C114">
-        <v>142</v>
+        <v>98</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11885</v>
+        <v>11886</v>
       </c>
       <c r="B115">
         <v>2</v>
@@ -1650,43 +1650,43 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11886</v>
+        <v>11920</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>98</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11920</v>
+        <v>12010</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C117">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12010</v>
+        <v>12040</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C118">
-        <v>81</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12040</v>
+        <v>12050</v>
       </c>
       <c r="B119">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12050</v>
+        <v>12294</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -1705,21 +1705,21 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12294</v>
+        <v>12535</v>
       </c>
       <c r="B121">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12513</v>
+        <v>12538</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C122">
         <v>7</v>
@@ -1727,21 +1727,21 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12535</v>
+        <v>12721</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123">
-        <v>14</v>
+        <v>146</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12538</v>
+        <v>12923</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -1749,87 +1749,87 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12721</v>
+        <v>12924</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>144</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12764</v>
+        <v>12925</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>388</v>
+        <v>31</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12923</v>
+        <v>12979</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12979</v>
+        <v>13257</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C128">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13030</v>
+        <v>13258</v>
       </c>
       <c r="B129">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C129">
-        <v>75</v>
+        <v>360</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13257</v>
+        <v>13259</v>
       </c>
       <c r="B130">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C130">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13258</v>
+        <v>13260</v>
       </c>
       <c r="B131">
         <v>29</v>
       </c>
       <c r="C131">
-        <v>360</v>
+        <v>37</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13259</v>
+        <v>13264</v>
       </c>
       <c r="B132">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C132">
         <v>36</v>
@@ -1837,43 +1837,43 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13260</v>
+        <v>13269</v>
       </c>
       <c r="B133">
         <v>29</v>
       </c>
       <c r="C133">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13269</v>
+        <v>13272</v>
       </c>
       <c r="B134">
         <v>29</v>
       </c>
       <c r="C134">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13271</v>
+        <v>13928</v>
       </c>
       <c r="B135">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13272</v>
+        <v>13964</v>
       </c>
       <c r="B136">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C136">
         <v>52</v>
@@ -1881,87 +1881,87 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13276</v>
+        <v>13965</v>
       </c>
       <c r="B137">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>13964</v>
+        <v>19687</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>13967</v>
+        <v>19924</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>19924</v>
+        <v>20650</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>20650</v>
+        <v>20927</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>116</v>
+        <v>41</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>20927</v>
+        <v>21068</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C142">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21068</v>
+        <v>21454</v>
       </c>
       <c r="B143">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C143">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>21454</v>
+        <v>22324</v>
       </c>
       <c r="B144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C144">
         <v>7</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22324</v>
+        <v>22326</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -1980,7 +1980,7 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>22326</v>
+        <v>22327</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -1991,90 +1991,57 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>22327</v>
+        <v>23992</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23233</v>
+        <v>24566</v>
       </c>
       <c r="B148">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C148">
-        <v>48</v>
+        <v>165</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>23992</v>
+        <v>24567</v>
       </c>
       <c r="B149">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C149">
-        <v>27</v>
+        <v>176</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>23994</v>
+        <v>24669</v>
       </c>
       <c r="B150">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C150">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>24566</v>
+        <v>25278</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C151">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152">
-        <v>24567</v>
-      </c>
-      <c r="B152">
-        <v>1</v>
-      </c>
-      <c r="C152">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153">
-        <v>24669</v>
-      </c>
-      <c r="B153">
-        <v>1</v>
-      </c>
-      <c r="C153">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154">
-        <v>24726</v>
-      </c>
-      <c r="B154">
-        <v>2</v>
-      </c>
-      <c r="C154">
-        <v>7</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -407,98 +407,98 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>30</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>44</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>144</v>
+        <v>308</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>145</v>
+        <v>345</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>78</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>146</v>
+        <v>413</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>80</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>201</v>
+        <v>566</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>164</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>216</v>
+        <v>615</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>217</v>
+        <v>788</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -506,87 +506,87 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>248</v>
+        <v>947</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>305</v>
+        <v>949</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>76</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>308</v>
+        <v>957</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>85</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>345</v>
+        <v>965</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>218</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>362</v>
+        <v>976</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>378</v>
+        <v>1051</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>92</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>413</v>
+        <v>1054</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>86</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>417</v>
+        <v>1060</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
         <v>7</v>
@@ -594,32 +594,32 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>435</v>
+        <v>1309</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>440</v>
+        <v>1448</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>101</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>566</v>
+        <v>1454</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22">
         <v>7</v>
@@ -627,54 +627,54 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>589</v>
+        <v>1576</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>131</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>593</v>
+        <v>1654</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>114</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>616</v>
+        <v>1655</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>624</v>
+        <v>1656</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>738</v>
+        <v>2013</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>7</v>
@@ -682,54 +682,54 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>790</v>
+        <v>2049</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>949</v>
+        <v>2188</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>950</v>
+        <v>2216</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C30">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>965</v>
+        <v>2296</v>
       </c>
       <c r="B31">
         <v>10</v>
       </c>
       <c r="C31">
-        <v>296</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>976</v>
+        <v>2323</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -737,65 +737,65 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1309</v>
+        <v>2327</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>28</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1448</v>
+        <v>2421</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1490</v>
+        <v>2423</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C35">
-        <v>26</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1492</v>
+        <v>2424</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C36">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1654</v>
+        <v>2436</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1655</v>
+        <v>2492</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
         <v>7</v>
@@ -803,84 +803,84 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1656</v>
+        <v>2803</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>46</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1668</v>
+        <v>2934</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1728</v>
+        <v>2935</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2190</v>
+        <v>2990</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2327</v>
+        <v>2991</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2419</v>
+        <v>3021</v>
       </c>
       <c r="B44">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="C44">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2423</v>
+        <v>3024</v>
       </c>
       <c r="B45">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>94</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2436</v>
+        <v>3257</v>
       </c>
       <c r="B46">
         <v>4</v>
@@ -891,57 +891,57 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2438</v>
+        <v>3434</v>
       </c>
       <c r="B47">
         <v>2</v>
       </c>
       <c r="C47">
-        <v>326</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2934</v>
+        <v>3495</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2991</v>
+        <v>3581</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>96</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3434</v>
+        <v>3582</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3495</v>
+        <v>3584</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -952,70 +952,70 @@
         <v>1</v>
       </c>
       <c r="C52">
-        <v>80</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3955</v>
+        <v>3915</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C53">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>4019</v>
+        <v>3955</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>4222</v>
+        <v>4043</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>4223</v>
+        <v>4063</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>283</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>5111</v>
+        <v>4222</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C57">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5152</v>
+        <v>4223</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58">
         <v>7</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5153</v>
+        <v>5152</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5243</v>
+        <v>5153</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60">
         <v>7</v>
@@ -1045,87 +1045,87 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5453</v>
+        <v>5243</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>53</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5491</v>
+        <v>5540</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>49</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5493</v>
+        <v>5541</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>51</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5540</v>
+        <v>5577</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5541</v>
+        <v>5585</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5577</v>
+        <v>5853</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5585</v>
+        <v>6540</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5730</v>
+        <v>6627</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68">
         <v>7</v>
@@ -1133,274 +1133,274 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5736</v>
+        <v>6935</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>27</v>
+        <v>270</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>6097</v>
+        <v>7520</v>
       </c>
       <c r="B70">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>6098</v>
+        <v>7886</v>
       </c>
       <c r="B71">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="C71">
-        <v>39</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6158</v>
+        <v>8283</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>309</v>
+        <v>254</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>6540</v>
+        <v>8285</v>
       </c>
       <c r="B73">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>39</v>
+        <v>254</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6627</v>
+        <v>8649</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>7</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6931</v>
+        <v>8674</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>52</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6935</v>
+        <v>8676</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76">
-        <v>281</v>
+        <v>189</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6936</v>
+        <v>8688</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C77">
-        <v>138</v>
+        <v>195</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>7004</v>
+        <v>8753</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>40</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>7886</v>
+        <v>9065</v>
       </c>
       <c r="B79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>72</v>
+        <v>160</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8648</v>
+        <v>9070</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>184</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8649</v>
+        <v>9088</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C81">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8650</v>
+        <v>9373</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C82">
-        <v>123</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8672</v>
+        <v>9480</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>146</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8853</v>
+        <v>9507</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84">
-        <v>284</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8907</v>
+        <v>9529</v>
       </c>
       <c r="B85">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C85">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8915</v>
+        <v>9877</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C86">
-        <v>81</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8939</v>
+        <v>9996</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C87">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9208</v>
+        <v>10148</v>
       </c>
       <c r="B88">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9209</v>
+        <v>10149</v>
       </c>
       <c r="B89">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>200</v>
+        <v>474</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9239</v>
+        <v>10176</v>
       </c>
       <c r="B90">
         <v>29</v>
       </c>
       <c r="C90">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9358</v>
+        <v>10455</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C91">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9529</v>
+        <v>10514</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92">
-        <v>7</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>9530</v>
+        <v>10594</v>
       </c>
       <c r="B93">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10148</v>
+        <v>10596</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C94">
         <v>7</v>
@@ -1419,65 +1419,65 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10149</v>
+        <v>10605</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>10455</v>
+        <v>10716</v>
       </c>
       <c r="B96">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10514</v>
+        <v>10825</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>344</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10529</v>
+        <v>11151</v>
       </c>
       <c r="B98">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="C98">
-        <v>109</v>
+        <v>905</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10530</v>
+        <v>11212</v>
       </c>
       <c r="B99">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="C99">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10716</v>
+        <v>11410</v>
       </c>
       <c r="B100">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C100">
         <v>7</v>
@@ -1485,95 +1485,95 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10717</v>
+        <v>11450</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>64</v>
+        <v>260</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10825</v>
+        <v>11681</v>
       </c>
       <c r="B102">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>8</v>
+        <v>278</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11151</v>
+        <v>11690</v>
       </c>
       <c r="B103">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>967</v>
+        <v>160</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11212</v>
+        <v>11737</v>
       </c>
       <c r="B104">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>129</v>
+        <v>31</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11396</v>
+        <v>11844</v>
       </c>
       <c r="B105">
         <v>2</v>
       </c>
       <c r="C105">
-        <v>46</v>
+        <v>139</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11410</v>
+        <v>11885</v>
       </c>
       <c r="B106">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>8</v>
+        <v>98</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11685</v>
+        <v>11886</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107">
-        <v>271</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11738</v>
+        <v>11911</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11773</v>
+        <v>11920</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -1584,76 +1584,76 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11835</v>
+        <v>12010</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C110">
-        <v>128</v>
+        <v>81</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11837</v>
+        <v>12040</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C111">
-        <v>130</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11838</v>
+        <v>12048</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>131</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11844</v>
+        <v>12050</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>142</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11885</v>
+        <v>12243</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C114">
-        <v>98</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11886</v>
+        <v>12269</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115">
-        <v>98</v>
+        <v>36</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11920</v>
+        <v>12294</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C116">
         <v>7</v>
@@ -1661,32 +1661,32 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12010</v>
+        <v>12304</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>81</v>
+        <v>56</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12040</v>
+        <v>12535</v>
       </c>
       <c r="B118">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12050</v>
+        <v>12538</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -1694,266 +1694,266 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12294</v>
+        <v>12546</v>
       </c>
       <c r="B120">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12535</v>
+        <v>12663</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12538</v>
+        <v>12791</v>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>409</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12721</v>
+        <v>13030</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C123">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12923</v>
+        <v>13114</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12924</v>
+        <v>13269</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C125">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12925</v>
+        <v>13272</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C126">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12979</v>
+        <v>13273</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C127">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13257</v>
+        <v>13293</v>
       </c>
       <c r="B128">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C128">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13258</v>
+        <v>13402</v>
       </c>
       <c r="B129">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>360</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13259</v>
+        <v>13403</v>
       </c>
       <c r="B130">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13260</v>
+        <v>13406</v>
       </c>
       <c r="B131">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13264</v>
+        <v>13407</v>
       </c>
       <c r="B132">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13269</v>
+        <v>13964</v>
       </c>
       <c r="B133">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>39</v>
+        <v>101</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13272</v>
+        <v>13968</v>
       </c>
       <c r="B134">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>52</v>
+        <v>68</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13928</v>
+        <v>19883</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13964</v>
+        <v>19924</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13965</v>
+        <v>20650</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>19687</v>
+        <v>21068</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C138">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>19924</v>
+        <v>21745</v>
       </c>
       <c r="B139">
         <v>2</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>20650</v>
+        <v>21789</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>63</v>
+        <v>47</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>20927</v>
+        <v>22086</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C141">
-        <v>41</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21068</v>
+        <v>22087</v>
       </c>
       <c r="B142">
         <v>10</v>
       </c>
       <c r="C142">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21454</v>
+        <v>22088</v>
       </c>
       <c r="B143">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -1969,7 +1969,7 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22326</v>
+        <v>22361</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -1980,54 +1980,54 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>22327</v>
+        <v>22407</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23992</v>
+        <v>22888</v>
       </c>
       <c r="B147">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C147">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>24566</v>
+        <v>23233</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C148">
-        <v>165</v>
+        <v>47</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>24567</v>
+        <v>23661</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>24669</v>
+        <v>23662</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C150">
         <v>7</v>
@@ -2035,13 +2035,101 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>25278</v>
+        <v>24254</v>
       </c>
       <c r="B151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C151">
-        <v>145</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>24258</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+      <c r="C152">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>24566</v>
+      </c>
+      <c r="B153">
+        <v>1</v>
+      </c>
+      <c r="C153">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>24567</v>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+      <c r="C154">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155">
+        <v>24669</v>
+      </c>
+      <c r="B155">
+        <v>1</v>
+      </c>
+      <c r="C155">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156">
+        <v>24670</v>
+      </c>
+      <c r="B156">
+        <v>1</v>
+      </c>
+      <c r="C156">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157">
+        <v>24726</v>
+      </c>
+      <c r="B157">
+        <v>2</v>
+      </c>
+      <c r="C157">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158">
+        <v>25698</v>
+      </c>
+      <c r="B158">
+        <v>3</v>
+      </c>
+      <c r="C158">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159">
+        <v>25960</v>
+      </c>
+      <c r="B159">
+        <v>2</v>
+      </c>
+      <c r="C159">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,18 +402,18 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>62</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>78</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -424,78 +424,78 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>377</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>308</v>
+        <v>216</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>85</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>321</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>413</v>
+        <v>334</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>566</v>
+        <v>362</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>615</v>
+        <v>416</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>788</v>
+        <v>566</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -506,172 +506,172 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>947</v>
+        <v>788</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B13">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>965</v>
+        <v>950</v>
       </c>
       <c r="B15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>302</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>976</v>
+        <v>965</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>1051</v>
+        <v>972</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>26</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>156</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1060</v>
+        <v>1051</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1309</v>
+        <v>1054</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>28</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1448</v>
+        <v>1060</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1454</v>
+        <v>1448</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1576</v>
+        <v>1454</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1654</v>
+        <v>1576</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>2013</v>
+        <v>1656</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -682,101 +682,101 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>2049</v>
+        <v>1728</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>278</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>2188</v>
+        <v>2013</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>2216</v>
+        <v>2054</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>466</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2296</v>
+        <v>2057</v>
       </c>
       <c r="B31">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2323</v>
+        <v>2216</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2327</v>
+        <v>2296</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C33">
-        <v>68</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2421</v>
+        <v>2308</v>
       </c>
       <c r="B34">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C34">
-        <v>112</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2423</v>
+        <v>2323</v>
       </c>
       <c r="B35">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>94</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2424</v>
+        <v>2327</v>
       </c>
       <c r="B36">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -787,18 +787,18 @@
         <v>4</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2492</v>
+        <v>2438</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>753</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -820,7 +820,7 @@
         <v>1</v>
       </c>
       <c r="C40">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -831,7 +831,7 @@
         <v>1</v>
       </c>
       <c r="C41">
-        <v>18</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -842,7 +842,7 @@
         <v>3</v>
       </c>
       <c r="C42">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -853,48 +853,48 @@
         <v>3</v>
       </c>
       <c r="C43">
-        <v>75</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>3021</v>
+        <v>3016</v>
       </c>
       <c r="B44">
         <v>68</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>3024</v>
+        <v>3021</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C45">
-        <v>137</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>3257</v>
+        <v>3024</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3434</v>
+        <v>3257</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C47">
         <v>7</v>
@@ -902,40 +902,40 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3495</v>
+        <v>3434</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3581</v>
+        <v>3477</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3582</v>
+        <v>3495</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3584</v>
+        <v>3581</v>
       </c>
       <c r="B51">
         <v>3</v>
@@ -946,21 +946,21 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3894</v>
+        <v>3582</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3915</v>
+        <v>3584</v>
       </c>
       <c r="B53">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C53">
         <v>7</v>
@@ -968,51 +968,51 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3955</v>
+        <v>3894</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>4043</v>
+        <v>3915</v>
       </c>
       <c r="B55">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C55">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>4063</v>
+        <v>3955</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>283</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4222</v>
+        <v>4063</v>
       </c>
       <c r="B57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4223</v>
+        <v>4222</v>
       </c>
       <c r="B58">
         <v>4</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5152</v>
+        <v>4223</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C59">
         <v>7</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5153</v>
+        <v>5152</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -1045,252 +1045,252 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5243</v>
+        <v>5153</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>126</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5540</v>
+        <v>5243</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C62">
-        <v>85</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5541</v>
+        <v>5493</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5577</v>
+        <v>5541</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>111</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5585</v>
+        <v>5577</v>
       </c>
       <c r="B65">
         <v>3</v>
       </c>
       <c r="C65">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5853</v>
+        <v>5585</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C66">
-        <v>85</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>6540</v>
+        <v>6158</v>
       </c>
       <c r="B67">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>39</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>6627</v>
+        <v>6540</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>6935</v>
+        <v>6936</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>270</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>7520</v>
+        <v>7084</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>7886</v>
+        <v>7520</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>72</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>8283</v>
+        <v>7629</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>254</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>8285</v>
+        <v>7886</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C73">
-        <v>254</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>8649</v>
+        <v>7887</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C74">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>8674</v>
+        <v>8155</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C75">
-        <v>141</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>8676</v>
+        <v>8216</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>189</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8688</v>
+        <v>8649</v>
       </c>
       <c r="B77">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>195</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8753</v>
+        <v>8676</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>9065</v>
+        <v>8688</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C79">
-        <v>160</v>
+        <v>195</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>9070</v>
+        <v>8753</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>17</v>
+        <v>182</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>9088</v>
+        <v>8915</v>
       </c>
       <c r="B81">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>108</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>9373</v>
+        <v>9070</v>
       </c>
       <c r="B82">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>9480</v>
+        <v>9088</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C83">
         <v>7</v>
@@ -1298,21 +1298,21 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>9507</v>
+        <v>9373</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C84">
-        <v>103</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>9529</v>
+        <v>9480</v>
       </c>
       <c r="B85">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C85">
         <v>7</v>
@@ -1320,65 +1320,65 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>9877</v>
+        <v>9529</v>
       </c>
       <c r="B86">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C86">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9996</v>
+        <v>9623</v>
       </c>
       <c r="B87">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C87">
-        <v>69</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>10148</v>
+        <v>9840</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>423</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>10149</v>
+        <v>9877</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C89">
-        <v>474</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>10176</v>
+        <v>9996</v>
       </c>
       <c r="B90">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="C90">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>10455</v>
+        <v>10148</v>
       </c>
       <c r="B91">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C91">
         <v>7</v>
@@ -1386,21 +1386,21 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>10514</v>
+        <v>10176</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C92">
-        <v>177</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10594</v>
+        <v>10455</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10596</v>
+        <v>10467</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C94">
         <v>7</v>
@@ -1419,186 +1419,186 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10605</v>
+        <v>10514</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>7</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>10716</v>
+        <v>10574</v>
       </c>
       <c r="B96">
         <v>3</v>
       </c>
       <c r="C96">
-        <v>52</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10825</v>
+        <v>10594</v>
       </c>
       <c r="B97">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>344</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>11151</v>
+        <v>10596</v>
       </c>
       <c r="B98">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>905</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>11212</v>
+        <v>10605</v>
       </c>
       <c r="B99">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>115</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>11410</v>
+        <v>10825</v>
       </c>
       <c r="B100">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>343</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11450</v>
+        <v>10994</v>
       </c>
       <c r="B101">
         <v>2</v>
       </c>
       <c r="C101">
-        <v>260</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11681</v>
+        <v>11151</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C102">
-        <v>278</v>
+        <v>932</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11690</v>
+        <v>11212</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C103">
-        <v>160</v>
+        <v>121</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11737</v>
+        <v>11410</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C104">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11844</v>
+        <v>11450</v>
       </c>
       <c r="B105">
         <v>2</v>
       </c>
       <c r="C105">
-        <v>139</v>
+        <v>248</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11885</v>
+        <v>11738</v>
       </c>
       <c r="B106">
         <v>2</v>
       </c>
       <c r="C106">
-        <v>98</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11886</v>
+        <v>11739</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107">
-        <v>98</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11911</v>
+        <v>11844</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>140</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11920</v>
+        <v>11885</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>7</v>
+        <v>97</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>12010</v>
+        <v>11911</v>
       </c>
       <c r="B110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>81</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>12040</v>
+        <v>11920</v>
       </c>
       <c r="B111">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C111">
         <v>7</v>
@@ -1606,32 +1606,32 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>12048</v>
+        <v>11961</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>12050</v>
+        <v>12010</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>12243</v>
+        <v>12040</v>
       </c>
       <c r="B114">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C114">
         <v>7</v>
@@ -1639,21 +1639,21 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12269</v>
+        <v>12048</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12294</v>
+        <v>12050</v>
       </c>
       <c r="B116">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C116">
         <v>7</v>
@@ -1661,32 +1661,32 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12304</v>
+        <v>12252</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C117">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12535</v>
+        <v>12269</v>
       </c>
       <c r="B118">
         <v>2</v>
       </c>
       <c r="C118">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12538</v>
+        <v>12294</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -1694,76 +1694,76 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12546</v>
+        <v>12304</v>
       </c>
       <c r="B120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12663</v>
+        <v>12535</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12791</v>
+        <v>12538</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C122">
-        <v>409</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>13030</v>
+        <v>12546</v>
       </c>
       <c r="B123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C123">
-        <v>154</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>13114</v>
+        <v>12663</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>13269</v>
+        <v>12791</v>
       </c>
       <c r="B125">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C125">
-        <v>8</v>
+        <v>417</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>13272</v>
+        <v>13114</v>
       </c>
       <c r="B126">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C126">
         <v>7</v>
@@ -1771,32 +1771,32 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>13273</v>
+        <v>13116</v>
       </c>
       <c r="B127">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13293</v>
+        <v>13269</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C128">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13402</v>
+        <v>13272</v>
       </c>
       <c r="B129">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C129">
         <v>7</v>
@@ -1804,18 +1804,18 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13403</v>
+        <v>13293</v>
       </c>
       <c r="B130">
         <v>3</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>326</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13406</v>
+        <v>13402</v>
       </c>
       <c r="B131">
         <v>3</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13407</v>
+        <v>13403</v>
       </c>
       <c r="B132">
         <v>3</v>
@@ -1837,197 +1837,197 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13964</v>
+        <v>13406</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C133">
-        <v>101</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13968</v>
+        <v>13407</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C134">
-        <v>68</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>19883</v>
+        <v>13968</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>19924</v>
+        <v>18964</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>20650</v>
+        <v>19687</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>78</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>21068</v>
+        <v>19924</v>
       </c>
       <c r="B138">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C138">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21745</v>
+        <v>19969</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C139">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21789</v>
+        <v>20556</v>
       </c>
       <c r="B140">
         <v>2</v>
       </c>
       <c r="C140">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>22086</v>
+        <v>20650</v>
       </c>
       <c r="B141">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>8</v>
+        <v>117</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>22087</v>
+        <v>20927</v>
       </c>
       <c r="B142">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>22088</v>
+        <v>21068</v>
       </c>
       <c r="B143">
         <v>10</v>
       </c>
       <c r="C143">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>22324</v>
+        <v>21745</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22361</v>
+        <v>21789</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>22407</v>
+        <v>21793</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>22888</v>
+        <v>22086</v>
       </c>
       <c r="B147">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23233</v>
+        <v>22087</v>
       </c>
       <c r="B148">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C148">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>23661</v>
+        <v>22088</v>
       </c>
       <c r="B149">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C149">
-        <v>173</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>23662</v>
+        <v>22324</v>
       </c>
       <c r="B150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C150">
         <v>7</v>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>24254</v>
+        <v>22361</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2046,43 +2046,43 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>24258</v>
+        <v>22407</v>
       </c>
       <c r="B152">
         <v>1</v>
       </c>
       <c r="C152">
-        <v>72</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>24566</v>
+        <v>23233</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C153">
-        <v>167</v>
+        <v>48</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>24567</v>
+        <v>23329</v>
       </c>
       <c r="B154">
         <v>1</v>
       </c>
       <c r="C154">
-        <v>159</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>24669</v>
+        <v>23661</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C155">
         <v>7</v>
@@ -2090,21 +2090,21 @@
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>24670</v>
+        <v>23662</v>
       </c>
       <c r="B156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C156">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>24726</v>
+        <v>24254</v>
       </c>
       <c r="B157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C157">
         <v>7</v>
@@ -2112,24 +2112,79 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>25698</v>
+        <v>24256</v>
       </c>
       <c r="B158">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C158">
-        <v>382</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
+        <v>24258</v>
+      </c>
+      <c r="B159">
+        <v>1</v>
+      </c>
+      <c r="C159">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160">
+        <v>24566</v>
+      </c>
+      <c r="B160">
+        <v>1</v>
+      </c>
+      <c r="C160">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161">
+        <v>24567</v>
+      </c>
+      <c r="B161">
+        <v>1</v>
+      </c>
+      <c r="C161">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162">
+        <v>24669</v>
+      </c>
+      <c r="B162">
+        <v>1</v>
+      </c>
+      <c r="C162">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163">
+        <v>24726</v>
+      </c>
+      <c r="B163">
+        <v>2</v>
+      </c>
+      <c r="C163">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164">
         <v>25960</v>
       </c>
-      <c r="B159">
-        <v>2</v>
-      </c>
-      <c r="C159">
-        <v>137</v>
+      <c r="B164">
+        <v>2</v>
+      </c>
+      <c r="C164">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,109 +396,109 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>124</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>54</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>216</v>
+        <v>142</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>333</v>
+        <v>144</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>334</v>
+        <v>145</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>45</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>362</v>
+        <v>146</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>69</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>416</v>
+        <v>159</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>43</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>566</v>
+        <v>216</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -506,10 +506,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>788</v>
+        <v>248</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -517,51 +517,51 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>947</v>
+        <v>305</v>
       </c>
       <c r="B13">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>22</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>949</v>
+        <v>308</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>950</v>
+        <v>334</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C15">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>965</v>
+        <v>345</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>314</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>972</v>
+        <v>346</v>
       </c>
       <c r="B17">
         <v>3</v>
@@ -572,84 +572,84 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>976</v>
+        <v>361</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1051</v>
+        <v>362</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>27</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1054</v>
+        <v>412</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>160</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1060</v>
+        <v>416</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1448</v>
+        <v>417</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1454</v>
+        <v>523</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1576</v>
+        <v>566</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1654</v>
+        <v>788</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -660,109 +660,109 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1655</v>
+        <v>949</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1656</v>
+        <v>965</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1728</v>
+        <v>976</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>99</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>2013</v>
+        <v>1007</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>2054</v>
+        <v>1051</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>466</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2057</v>
+        <v>1060</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>236</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2216</v>
+        <v>1413</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32">
-        <v>13</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2296</v>
+        <v>1448</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2308</v>
+        <v>1454</v>
       </c>
       <c r="B34">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2323</v>
+        <v>1492</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35">
         <v>7</v>
@@ -770,109 +770,109 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2327</v>
+        <v>1576</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2436</v>
+        <v>1655</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2438</v>
+        <v>1728</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>753</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2803</v>
+        <v>1814</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2934</v>
+        <v>2013</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2935</v>
+        <v>2049</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>55</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2990</v>
+        <v>2054</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>465</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2991</v>
+        <v>2216</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C43">
-        <v>151</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>3016</v>
+        <v>2296</v>
       </c>
       <c r="B44">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="C44">
-        <v>60</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>3021</v>
+        <v>2323</v>
       </c>
       <c r="B45">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C45">
         <v>7</v>
@@ -880,84 +880,84 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>3024</v>
+        <v>2423</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C46">
-        <v>143</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3257</v>
+        <v>2424</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3434</v>
+        <v>2436</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3477</v>
+        <v>2438</v>
       </c>
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49">
-        <v>53</v>
+        <v>326</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3495</v>
+        <v>2778</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3581</v>
+        <v>2803</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3582</v>
+        <v>2859</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3584</v>
+        <v>2990</v>
       </c>
       <c r="B53">
         <v>3</v>
@@ -968,65 +968,65 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3894</v>
+        <v>3016</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3915</v>
+        <v>3024</v>
       </c>
       <c r="B55">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>147</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3955</v>
+        <v>3257</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4063</v>
+        <v>3434</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4222</v>
+        <v>3495</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4223</v>
+        <v>3581</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59">
         <v>7</v>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5152</v>
+        <v>3582</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60">
         <v>7</v>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5153</v>
+        <v>3584</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61">
         <v>7</v>
@@ -1056,351 +1056,351 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5243</v>
+        <v>3894</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>129</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5493</v>
+        <v>3915</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C63">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5541</v>
+        <v>3955</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5577</v>
+        <v>4063</v>
       </c>
       <c r="B65">
         <v>3</v>
       </c>
       <c r="C65">
-        <v>110</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5585</v>
+        <v>4222</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C66">
-        <v>135</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>6158</v>
+        <v>4223</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C67">
-        <v>134</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>6540</v>
+        <v>5152</v>
       </c>
       <c r="B68">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>6936</v>
+        <v>5153</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>7084</v>
+        <v>5243</v>
       </c>
       <c r="B70">
         <v>3</v>
       </c>
       <c r="C70">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>7520</v>
+        <v>5541</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>7629</v>
+        <v>5577</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>7886</v>
+        <v>5585</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>7887</v>
+        <v>5733</v>
       </c>
       <c r="B74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>71</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>8155</v>
+        <v>5812</v>
       </c>
       <c r="B75">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>298</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>8216</v>
+        <v>6540</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C76">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8649</v>
+        <v>7520</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>94</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8676</v>
+        <v>7887</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C78">
-        <v>188</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8688</v>
+        <v>8106</v>
       </c>
       <c r="B79">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C79">
-        <v>195</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8753</v>
+        <v>8216</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>182</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8915</v>
+        <v>8284</v>
       </c>
       <c r="B81">
         <v>2</v>
       </c>
       <c r="C81">
-        <v>78</v>
+        <v>243</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>9070</v>
+        <v>8649</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>16</v>
+        <v>96</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>9088</v>
+        <v>8674</v>
       </c>
       <c r="B83">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>7</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>9373</v>
+        <v>8676</v>
       </c>
       <c r="B84">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>7</v>
+        <v>188</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>9480</v>
+        <v>8923</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>9529</v>
+        <v>9070</v>
       </c>
       <c r="B86">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9623</v>
+        <v>9088</v>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C87">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9840</v>
+        <v>9480</v>
       </c>
       <c r="B88">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>423</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9877</v>
+        <v>9507</v>
       </c>
       <c r="B89">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>21</v>
+        <v>200</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9996</v>
+        <v>9529</v>
       </c>
       <c r="B90">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>69</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>10148</v>
+        <v>9840</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>439</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>10176</v>
+        <v>9996</v>
       </c>
       <c r="B92">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="C92">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10455</v>
+        <v>10148</v>
       </c>
       <c r="B93">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -1408,43 +1408,43 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10467</v>
+        <v>10149</v>
       </c>
       <c r="B94">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10514</v>
+        <v>10176</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C95">
-        <v>172</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>10574</v>
+        <v>10455</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C96">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10594</v>
+        <v>10467</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -1452,21 +1452,21 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10596</v>
+        <v>10514</v>
       </c>
       <c r="B98">
         <v>3</v>
       </c>
       <c r="C98">
-        <v>7</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10605</v>
+        <v>10594</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C99">
         <v>7</v>
@@ -1474,164 +1474,164 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10825</v>
+        <v>10596</v>
       </c>
       <c r="B100">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C100">
-        <v>343</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10994</v>
+        <v>10597</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>28</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11151</v>
+        <v>10598</v>
       </c>
       <c r="B102">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C102">
-        <v>932</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11212</v>
+        <v>10605</v>
       </c>
       <c r="B103">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>121</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11410</v>
+        <v>10825</v>
       </c>
       <c r="B104">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11450</v>
+        <v>10994</v>
       </c>
       <c r="B105">
         <v>2</v>
       </c>
       <c r="C105">
-        <v>248</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11738</v>
+        <v>11151</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C106">
-        <v>30</v>
+        <v>933</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11739</v>
+        <v>11212</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C107">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11844</v>
+        <v>11410</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C108">
-        <v>140</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11885</v>
+        <v>11450</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>97</v>
+        <v>254</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11911</v>
+        <v>11738</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11920</v>
+        <v>11885</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11961</v>
+        <v>11886</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>55</v>
+        <v>128</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>12010</v>
+        <v>11911</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>12040</v>
+        <v>11920</v>
       </c>
       <c r="B114">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C114">
         <v>7</v>
@@ -1639,21 +1639,21 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12048</v>
+        <v>12010</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C115">
-        <v>8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12050</v>
+        <v>12040</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C116">
         <v>7</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12252</v>
+        <v>12048</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C117">
         <v>7</v>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12269</v>
+        <v>12050</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C118">
         <v>7</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12294</v>
+        <v>12269</v>
       </c>
       <c r="B119">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -1694,13 +1694,13 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12304</v>
+        <v>12294</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C120">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -1711,7 +1711,7 @@
         <v>2</v>
       </c>
       <c r="C121">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -1755,70 +1755,70 @@
         <v>2</v>
       </c>
       <c r="C125">
-        <v>417</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>13114</v>
+        <v>12979</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>13116</v>
+        <v>13114</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13269</v>
+        <v>13116</v>
       </c>
       <c r="B128">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13272</v>
+        <v>13258</v>
       </c>
       <c r="B129">
         <v>29</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>360</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13293</v>
+        <v>13269</v>
       </c>
       <c r="B130">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C130">
-        <v>326</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13402</v>
+        <v>13272</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C131">
         <v>7</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13403</v>
+        <v>13402</v>
       </c>
       <c r="B132">
         <v>3</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13406</v>
+        <v>13403</v>
       </c>
       <c r="B133">
         <v>3</v>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13407</v>
+        <v>13406</v>
       </c>
       <c r="B134">
         <v>3</v>
@@ -1859,62 +1859,62 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13968</v>
+        <v>13407</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C135">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>18964</v>
+        <v>13964</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>33</v>
+        <v>51</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>19687</v>
+        <v>13968</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>19924</v>
+        <v>18964</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>19969</v>
+        <v>19687</v>
       </c>
       <c r="B139">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C139">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>20556</v>
+        <v>19924</v>
       </c>
       <c r="B140">
         <v>2</v>
@@ -1925,167 +1925,167 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>20650</v>
+        <v>19986</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141">
-        <v>117</v>
+        <v>28</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>20927</v>
+        <v>20556</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C142">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21068</v>
+        <v>20650</v>
       </c>
       <c r="B143">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C143">
-        <v>15</v>
+        <v>118</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>21745</v>
+        <v>20927</v>
       </c>
       <c r="B144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C144">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>21789</v>
+        <v>21068</v>
       </c>
       <c r="B145">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C145">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>21793</v>
+        <v>21745</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>22086</v>
+        <v>21789</v>
       </c>
       <c r="B147">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C147">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>22087</v>
+        <v>21793</v>
       </c>
       <c r="B148">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C148">
-        <v>10</v>
+        <v>241</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>22088</v>
+        <v>22086</v>
       </c>
       <c r="B149">
         <v>10</v>
       </c>
       <c r="C149">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>22324</v>
+        <v>22087</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C150">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>22361</v>
+        <v>22088</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C151">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>22407</v>
+        <v>22361</v>
       </c>
       <c r="B152">
         <v>1</v>
       </c>
       <c r="C152">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>23233</v>
+        <v>22407</v>
       </c>
       <c r="B153">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C153">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>23329</v>
+        <v>23233</v>
       </c>
       <c r="B154">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C154">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>23661</v>
+        <v>23329</v>
       </c>
       <c r="B155">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C155">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2096,7 +2096,7 @@
         <v>2</v>
       </c>
       <c r="C156">
-        <v>7</v>
+        <v>104</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2112,79 +2112,57 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>24256</v>
+        <v>24567</v>
       </c>
       <c r="B158">
         <v>1</v>
       </c>
       <c r="C158">
-        <v>7</v>
+        <v>168</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>24258</v>
+        <v>24669</v>
       </c>
       <c r="B159">
         <v>1</v>
       </c>
       <c r="C159">
-        <v>73</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>24566</v>
+        <v>24726</v>
       </c>
       <c r="B160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C160">
-        <v>171</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>24567</v>
+        <v>25958</v>
       </c>
       <c r="B161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C161">
-        <v>325</v>
+        <v>133</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>24669</v>
+        <v>25960</v>
       </c>
       <c r="B162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C162">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3">
-      <c r="A163">
-        <v>24726</v>
-      </c>
-      <c r="B163">
-        <v>2</v>
-      </c>
-      <c r="C163">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164">
-        <v>25960</v>
-      </c>
-      <c r="B164">
-        <v>2</v>
-      </c>
-      <c r="C164">
-        <v>180</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1126.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C162"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,7 +402,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -413,7 +413,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -424,23 +424,23 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>77</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -462,134 +462,134 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>78</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>146</v>
+        <v>206</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>363</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>74</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C14">
-        <v>84</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B15">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>369</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>303</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>362</v>
+        <v>411</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>70</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -605,65 +605,65 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21">
-        <v>42</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>523</v>
+        <v>416</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>77</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>566</v>
+        <v>434</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>788</v>
+        <v>435</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>949</v>
+        <v>566</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C26">
         <v>7</v>
@@ -671,21 +671,21 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>965</v>
+        <v>788</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>976</v>
+        <v>949</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -693,73 +693,73 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1007</v>
+        <v>956</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>137</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1051</v>
+        <v>957</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1060</v>
+        <v>965</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1413</v>
+        <v>976</v>
       </c>
       <c r="B32">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>1224</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1448</v>
+        <v>1007</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>20</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1454</v>
+        <v>1051</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1492</v>
+        <v>1060</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -770,241 +770,241 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1576</v>
+        <v>1163</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>24</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1655</v>
+        <v>1309</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1728</v>
+        <v>1414</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1814</v>
+        <v>1448</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2013</v>
+        <v>1576</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2049</v>
+        <v>1655</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>277</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2054</v>
+        <v>1668</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>465</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2216</v>
+        <v>1728</v>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2296</v>
+        <v>1886</v>
       </c>
       <c r="B44">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2323</v>
+        <v>2057</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2423</v>
+        <v>2188</v>
       </c>
       <c r="B46">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>94</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2424</v>
+        <v>2216</v>
       </c>
       <c r="B47">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C47">
-        <v>86</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2436</v>
+        <v>2296</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C48">
-        <v>61</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2438</v>
+        <v>2323</v>
       </c>
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49">
-        <v>326</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2778</v>
+        <v>2331</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>69</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2803</v>
+        <v>2421</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C51">
-        <v>14</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2859</v>
+        <v>2423</v>
       </c>
       <c r="B52">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="C52">
-        <v>36</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2990</v>
+        <v>2436</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3016</v>
+        <v>2438</v>
       </c>
       <c r="B54">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>28</v>
+        <v>331</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3024</v>
+        <v>2778</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>147</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3257</v>
+        <v>2803</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3434</v>
+        <v>2990</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -1012,54 +1012,54 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3495</v>
+        <v>3257</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3581</v>
+        <v>3338</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3582</v>
+        <v>3434</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3584</v>
+        <v>3495</v>
       </c>
       <c r="B61">
         <v>3</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3894</v>
+        <v>3581</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C62">
         <v>7</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3915</v>
+        <v>3582</v>
       </c>
       <c r="B63">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C63">
         <v>7</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3955</v>
+        <v>3584</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64">
         <v>7</v>
@@ -1089,21 +1089,21 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>4063</v>
+        <v>3894</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>4222</v>
+        <v>3915</v>
       </c>
       <c r="B66">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C66">
         <v>7</v>
@@ -1111,32 +1111,32 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>4223</v>
+        <v>3955</v>
       </c>
       <c r="B67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5152</v>
+        <v>4063</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5153</v>
+        <v>4222</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C69">
         <v>7</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5243</v>
+        <v>4223</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C70">
         <v>7</v>
@@ -1155,18 +1155,18 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5541</v>
+        <v>5152</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5577</v>
+        <v>5243</v>
       </c>
       <c r="B72">
         <v>3</v>
@@ -1177,263 +1177,263 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5585</v>
+        <v>5491</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5733</v>
+        <v>5541</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5812</v>
+        <v>5577</v>
       </c>
       <c r="B75">
         <v>3</v>
       </c>
       <c r="C75">
-        <v>298</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6540</v>
+        <v>5585</v>
       </c>
       <c r="B76">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C76">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7520</v>
+        <v>5729</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>7887</v>
+        <v>6496</v>
       </c>
       <c r="B78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8106</v>
+        <v>6540</v>
       </c>
       <c r="B79">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C79">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8216</v>
+        <v>7005</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8284</v>
+        <v>7084</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81">
-        <v>243</v>
+        <v>64</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8649</v>
+        <v>7520</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>96</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8674</v>
+        <v>8106</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C83">
-        <v>141</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8676</v>
+        <v>8216</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>188</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8923</v>
+        <v>8284</v>
       </c>
       <c r="B85">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>16</v>
+        <v>243</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>9070</v>
+        <v>8648</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9088</v>
+        <v>8649</v>
       </c>
       <c r="B87">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>91</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9480</v>
+        <v>8650</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9507</v>
+        <v>8674</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>200</v>
+        <v>141</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9529</v>
+        <v>8676</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>7</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9840</v>
+        <v>8923</v>
       </c>
       <c r="B91">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C91">
-        <v>439</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9996</v>
+        <v>9070</v>
       </c>
       <c r="B92">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>69</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10148</v>
+        <v>9081</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>240</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10149</v>
+        <v>9209</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C94">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10176</v>
+        <v>9239</v>
       </c>
       <c r="B95">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C95">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>10455</v>
+        <v>9529</v>
       </c>
       <c r="B96">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C96">
         <v>7</v>
@@ -1441,32 +1441,32 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10467</v>
+        <v>10148</v>
       </c>
       <c r="B97">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10514</v>
+        <v>10455</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C98">
-        <v>177</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10594</v>
+        <v>10467</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C99">
         <v>7</v>
@@ -1474,161 +1474,161 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10596</v>
+        <v>10514</v>
       </c>
       <c r="B100">
         <v>3</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>178</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10597</v>
+        <v>10596</v>
       </c>
       <c r="B101">
         <v>3</v>
       </c>
       <c r="C101">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10598</v>
+        <v>10825</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10605</v>
+        <v>10994</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10825</v>
+        <v>11151</v>
       </c>
       <c r="B104">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C104">
-        <v>8</v>
+        <v>934</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10994</v>
+        <v>11212</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C105">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11151</v>
+        <v>11290</v>
       </c>
       <c r="B106">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>933</v>
+        <v>48</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11212</v>
+        <v>11396</v>
       </c>
       <c r="B107">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11410</v>
+        <v>11403</v>
       </c>
       <c r="B108">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11450</v>
+        <v>11410</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C109">
-        <v>254</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11738</v>
+        <v>11450</v>
       </c>
       <c r="B110">
         <v>2</v>
       </c>
       <c r="C110">
-        <v>30</v>
+        <v>249</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11885</v>
+        <v>11492</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>96</v>
+        <v>44</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11886</v>
+        <v>11493</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>128</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11911</v>
+        <v>11885</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11920</v>
+        <v>11911</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -1639,32 +1639,32 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12010</v>
+        <v>11920</v>
       </c>
       <c r="B115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12040</v>
+        <v>12010</v>
       </c>
       <c r="B116">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12048</v>
+        <v>12040</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C117">
         <v>7</v>
@@ -1672,7 +1672,7 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12050</v>
+        <v>12048</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12269</v>
+        <v>12050</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -1711,7 +1711,7 @@
         <v>2</v>
       </c>
       <c r="C121">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -1727,84 +1727,84 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12546</v>
+        <v>12721</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123">
-        <v>7</v>
+        <v>283</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12663</v>
+        <v>12791</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
-        <v>7</v>
+        <v>415</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12791</v>
+        <v>12979</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12979</v>
+        <v>13114</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>13114</v>
+        <v>13116</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13116</v>
+        <v>13258</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C128">
-        <v>24</v>
+        <v>360</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13258</v>
+        <v>13269</v>
       </c>
       <c r="B129">
         <v>29</v>
       </c>
       <c r="C129">
-        <v>360</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13269</v>
+        <v>13272</v>
       </c>
       <c r="B130">
         <v>29</v>
@@ -1815,13 +1815,13 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13272</v>
+        <v>13276</v>
       </c>
       <c r="B131">
         <v>29</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -1859,18 +1859,18 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13407</v>
+        <v>13964</v>
       </c>
       <c r="B135">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13964</v>
+        <v>13968</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -1881,227 +1881,227 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13968</v>
+        <v>18964</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>18964</v>
+        <v>19687</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>19687</v>
+        <v>19924</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>19924</v>
+        <v>19986</v>
       </c>
       <c r="B140">
         <v>2</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>19986</v>
+        <v>20556</v>
       </c>
       <c r="B141">
         <v>2</v>
       </c>
       <c r="C141">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>20556</v>
+        <v>20650</v>
       </c>
       <c r="B142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>7</v>
+        <v>118</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>20650</v>
+        <v>20927</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143">
-        <v>118</v>
+        <v>40</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>20927</v>
+        <v>21068</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C144">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>21068</v>
+        <v>21745</v>
       </c>
       <c r="B145">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C145">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>21745</v>
+        <v>21789</v>
       </c>
       <c r="B146">
         <v>2</v>
       </c>
       <c r="C146">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>21789</v>
+        <v>22086</v>
       </c>
       <c r="B147">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C147">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>21793</v>
+        <v>22087</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C148">
-        <v>241</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>22086</v>
+        <v>22088</v>
       </c>
       <c r="B149">
         <v>10</v>
       </c>
       <c r="C149">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>22087</v>
+        <v>22361</v>
       </c>
       <c r="B150">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C150">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>22088</v>
+        <v>23233</v>
       </c>
       <c r="B151">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C151">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>22361</v>
+        <v>23662</v>
       </c>
       <c r="B152">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C152">
-        <v>7</v>
+        <v>104</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>22407</v>
+        <v>24254</v>
       </c>
       <c r="B153">
         <v>1</v>
       </c>
       <c r="C153">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>23233</v>
+        <v>24256</v>
       </c>
       <c r="B154">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C154">
-        <v>48</v>
+        <v>96</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>23329</v>
+        <v>24257</v>
       </c>
       <c r="B155">
         <v>1</v>
       </c>
       <c r="C155">
-        <v>10</v>
+        <v>71</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>23662</v>
+        <v>24567</v>
       </c>
       <c r="B156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C156">
-        <v>104</v>
+        <v>155</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>24254</v>
+        <v>24669</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2112,57 +2112,13 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>24567</v>
+        <v>24726</v>
       </c>
       <c r="B158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C158">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159">
-        <v>24669</v>
-      </c>
-      <c r="B159">
-        <v>1</v>
-      </c>
-      <c r="C159">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160">
-        <v>24726</v>
-      </c>
-      <c r="B160">
-        <v>2</v>
-      </c>
-      <c r="C160">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3">
-      <c r="A161">
-        <v>25958</v>
-      </c>
-      <c r="B161">
-        <v>2</v>
-      </c>
-      <c r="C161">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162">
-        <v>25960</v>
-      </c>
-      <c r="B162">
-        <v>2</v>
-      </c>
-      <c r="C162">
-        <v>135</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
